--- a/data/manualdata/_manualdata_master.xlsx
+++ b/data/manualdata/_manualdata_master.xlsx
@@ -5,17 +5,30 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\notebookpick\data\basedata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\notebookpick\data\manualdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{17E60DB4-2F3B-47DB-9F05-5877B18A4105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED65DED-2281-4195-BBE6-362A6B647278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{52B35C0C-4AC1-4CD7-A119-F59BBD510595}"/>
   </bookViews>
   <sheets>
     <sheet name="전체" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1414,14 +1427,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyFill="1">
@@ -1804,14 +1814,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50411788-00EA-46D9-AD03-A2E5A7239D60}">
   <dimension ref="A1:AD80"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.92578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1903,11 +1913,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>18</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>226</v>
       </c>
       <c r="C2" t="s">
@@ -1972,31 +1982,31 @@
         <v>217</v>
       </c>
       <c r="Z2">
-        <f>T2/W2</f>
+        <f t="shared" ref="Z2:Z33" si="0">T2/W2</f>
         <v>7.8947368421052628</v>
       </c>
       <c r="AA2">
-        <f>Z2-(AVERAGE(Z:Z))</f>
+        <f t="shared" ref="AA2:AA33" si="1">Z2-(AVERAGE(Z:Z))</f>
         <v>0.45561621342516823</v>
       </c>
       <c r="AB2">
-        <f>R2-AVERAGE(R:R)</f>
+        <f t="shared" ref="AB2:AB33" si="2">R2-AVERAGE(R:R)</f>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC2">
-        <f>S2/(-110+17.25*Q2)*100-100</f>
+        <f t="shared" ref="AC2:AC33" si="3">S2/(-110+17.25*Q2)*100-100</f>
         <v>-9.6385542168674618</v>
       </c>
       <c r="AD2">
-        <f>V2-AVERAGE(V:V)</f>
+        <f t="shared" ref="AD2:AD33" si="4">V2-AVERAGE(V:V)</f>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>65</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>216</v>
       </c>
       <c r="C3" t="s">
@@ -2021,7 +2031,7 @@
         <v>64</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K66" si="0">IF(X3&lt;&gt;"쿠팡", ((J3-I3)/I3)*100, "")</f>
+        <f t="shared" ref="K3:K66" si="5">IF(X3&lt;&gt;"쿠팡", ((J3-I3)/I3)*100, "")</f>
         <v>-11.111111111111111</v>
       </c>
       <c r="L3" t="s">
@@ -2064,31 +2074,31 @@
         <v>217</v>
       </c>
       <c r="Z3">
-        <f>T3/W3</f>
+        <f t="shared" si="0"/>
         <v>5.4545454545454541</v>
       </c>
       <c r="AA3">
-        <f>Z3-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-1.9845751741346405</v>
       </c>
       <c r="AB3">
-        <f>R3-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC3">
-        <f>S3/(-110+17.25*Q3)*100-100</f>
+        <f t="shared" si="3"/>
         <v>0.34889516530986953</v>
       </c>
       <c r="AD3">
-        <f>V3-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>66</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C4" t="s">
@@ -2110,7 +2120,7 @@
         <v>118</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-5.6000000000000005</v>
       </c>
       <c r="L4" t="s">
@@ -2153,27 +2163,27 @@
         <v>217</v>
       </c>
       <c r="Z4">
-        <f>T4/W4</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="AA4">
-        <f>Z4-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-1.4391206286800946</v>
       </c>
       <c r="AB4">
-        <f>R4-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC4">
-        <f>S4/(-110+17.25*Q4)*100-100</f>
+        <f t="shared" si="3"/>
         <v>1.8072289156626482</v>
       </c>
       <c r="AD4">
-        <f>V4-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>67</v>
       </c>
@@ -2202,7 +2212,7 @@
         <v>143</v>
       </c>
       <c r="K5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-10.625</v>
       </c>
       <c r="L5" t="s">
@@ -2245,31 +2255,31 @@
         <v>217</v>
       </c>
       <c r="Z5">
-        <f>T5/W5</f>
+        <f t="shared" si="0"/>
         <v>9.6551724137931032</v>
       </c>
       <c r="AA5">
-        <f>Z5-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>2.2160517851130086</v>
       </c>
       <c r="AB5">
-        <f>R5-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC5">
-        <f>S5/(-110+17.25*Q5)*100-100</f>
+        <f t="shared" si="3"/>
         <v>4.9429657794676842</v>
       </c>
       <c r="AD5">
-        <f>V5-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>76</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>218</v>
       </c>
       <c r="C6" t="s">
@@ -2294,7 +2304,7 @@
         <v>120</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-7.6923076923076925</v>
       </c>
       <c r="L6" t="s">
@@ -2337,27 +2347,27 @@
         <v>217</v>
       </c>
       <c r="Z6">
-        <f>T6/W6</f>
+        <f t="shared" si="0"/>
         <v>9.7560975609756095</v>
       </c>
       <c r="AA6">
-        <f>Z6-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>2.3169769322955149</v>
       </c>
       <c r="AB6">
-        <f>R6-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC6">
-        <f>S6/(-110+17.25*Q6)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-9.6385542168674618</v>
       </c>
       <c r="AD6">
-        <f>V6-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>77</v>
       </c>
@@ -2383,7 +2393,7 @@
         <v>76</v>
       </c>
       <c r="K7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>8.5714285714285712</v>
       </c>
       <c r="L7" t="s">
@@ -2426,27 +2436,27 @@
         <v>217</v>
       </c>
       <c r="Z7">
-        <f>T7/W7</f>
+        <f t="shared" si="0"/>
         <v>5.2682926829268295</v>
       </c>
       <c r="AA7">
-        <f>Z7-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-2.1708279457532651</v>
       </c>
       <c r="AB7">
-        <f>R7-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-3.5253164556962027</v>
       </c>
       <c r="AC7">
-        <f>S7/(-110+17.25*Q7)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-2.5769956002513936</v>
       </c>
       <c r="AD7">
-        <f>V7-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>79</v>
       </c>
@@ -2472,7 +2482,7 @@
         <v>196</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="L8" t="s">
@@ -2515,27 +2525,27 @@
         <v>217</v>
       </c>
       <c r="Z8">
-        <f>T8/W8</f>
+        <f t="shared" si="0"/>
         <v>10.133333333333333</v>
       </c>
       <c r="AA8">
-        <f>Z8-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>2.6942127046532383</v>
       </c>
       <c r="AB8">
-        <f>R8-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC8">
-        <f>S8/(-110+17.25*Q8)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-6.0240963855421654</v>
       </c>
       <c r="AD8">
-        <f>V8-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>78</v>
       </c>
@@ -2561,7 +2571,7 @@
         <v>180</v>
       </c>
       <c r="K9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>9.0909090909090917</v>
       </c>
       <c r="L9" t="s">
@@ -2604,27 +2614,27 @@
         <v>238</v>
       </c>
       <c r="Z9">
-        <f>T9/W9</f>
+        <f t="shared" si="0"/>
         <v>9.3333333333333339</v>
       </c>
       <c r="AA9">
-        <f>Z9-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>1.8942127046532393</v>
       </c>
       <c r="AB9">
-        <f>R9-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC9">
-        <f>S9/(-110+17.25*Q9)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-6.4638783269961948</v>
       </c>
       <c r="AD9">
-        <f>V9-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>64</v>
       </c>
@@ -2653,7 +2663,7 @@
         <v>170</v>
       </c>
       <c r="K10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>6.25</v>
       </c>
       <c r="L10" t="s">
@@ -2696,27 +2706,27 @@
         <v>208</v>
       </c>
       <c r="Z10">
-        <f>T10/W10</f>
+        <f t="shared" si="0"/>
         <v>9.1666666666666661</v>
       </c>
       <c r="AA10">
-        <f>Z10-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>1.7275460379865715</v>
       </c>
       <c r="AB10">
-        <f>R10-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-0.52531645569620267</v>
       </c>
       <c r="AC10">
-        <f>S10/(-110+17.25*Q10)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-17.940129788570232</v>
       </c>
       <c r="AD10">
-        <f>V10-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>63</v>
       </c>
@@ -2745,7 +2755,7 @@
         <v>117</v>
       </c>
       <c r="K11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-6.4</v>
       </c>
       <c r="L11" t="s">
@@ -2788,27 +2798,27 @@
         <v>208</v>
       </c>
       <c r="Z11">
-        <f>T11/W11</f>
+        <f t="shared" si="0"/>
         <v>8.5333333333333332</v>
       </c>
       <c r="AA11">
-        <f>Z11-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>1.0942127046532386</v>
       </c>
       <c r="AB11">
-        <f>R11-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>0.47468354430379733</v>
       </c>
       <c r="AC11">
-        <f>S11/(-110+17.25*Q11)*100-100</f>
+        <f t="shared" si="3"/>
         <v>2.409638554216869</v>
       </c>
       <c r="AD11">
-        <f>V11-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>61</v>
       </c>
@@ -2837,7 +2847,7 @@
         <v>185</v>
       </c>
       <c r="K12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-5.1282051282051277</v>
       </c>
       <c r="L12" t="s">
@@ -2880,27 +2890,27 @@
         <v>208</v>
       </c>
       <c r="Z12">
-        <f>T12/W12</f>
+        <f t="shared" si="0"/>
         <v>10.666666666666666</v>
       </c>
       <c r="AA12">
-        <f>Z12-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>3.2275460379865715</v>
       </c>
       <c r="AB12">
-        <f>R12-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC12">
-        <f>S12/(-110+17.25*Q12)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-9.0466136105246164</v>
       </c>
       <c r="AD12">
-        <f>V12-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>62</v>
       </c>
@@ -2929,7 +2939,7 @@
         <v>133</v>
       </c>
       <c r="K13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-1.4814814814814816</v>
       </c>
       <c r="L13" t="s">
@@ -2972,27 +2982,27 @@
         <v>208</v>
       </c>
       <c r="Z13">
-        <f>T13/W13</f>
+        <f t="shared" si="0"/>
         <v>9.481481481481481</v>
       </c>
       <c r="AA13">
-        <f>Z13-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>2.0423608528013864</v>
       </c>
       <c r="AB13">
-        <f>R13-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>0.47468354430379733</v>
       </c>
       <c r="AC13">
-        <f>S13/(-110+17.25*Q13)*100-100</f>
+        <f t="shared" si="3"/>
         <v>6.4638783269961948</v>
       </c>
       <c r="AD13">
-        <f>V13-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>4</v>
       </c>
@@ -3018,7 +3028,7 @@
         <v>48</v>
       </c>
       <c r="K14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L14" t="s">
@@ -3061,27 +3071,27 @@
         <v>34</v>
       </c>
       <c r="Z14">
-        <f>T14/W14</f>
+        <f t="shared" si="0"/>
         <v>5.6585365853658534</v>
       </c>
       <c r="AA14">
-        <f>Z14-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-1.7805840433142412</v>
       </c>
       <c r="AB14">
-        <f>R14-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-2.5253164556962027</v>
       </c>
       <c r="AC14">
-        <f>S14/(-110+17.25*Q14)*100-100</f>
+        <f t="shared" si="3"/>
         <v>2.409638554216869</v>
       </c>
       <c r="AD14">
-        <f>V14-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-3.924050632911392</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>5</v>
       </c>
@@ -3107,7 +3117,7 @@
         <v>55</v>
       </c>
       <c r="K15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L15" t="s">
@@ -3150,27 +3160,27 @@
         <v>34</v>
       </c>
       <c r="Z15">
-        <f>T15/W15</f>
+        <f t="shared" si="0"/>
         <v>5.6585365853658534</v>
       </c>
       <c r="AA15">
-        <f>Z15-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-1.7805840433142412</v>
       </c>
       <c r="AB15">
-        <f>R15-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-2.5253164556962027</v>
       </c>
       <c r="AC15">
-        <f>S15/(-110+17.25*Q15)*100-100</f>
+        <f t="shared" si="3"/>
         <v>2.409638554216869</v>
       </c>
       <c r="AD15">
-        <f>V15-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>3</v>
       </c>
@@ -3193,7 +3203,7 @@
         <v>75</v>
       </c>
       <c r="K16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L16" t="s">
@@ -3236,27 +3246,27 @@
         <v>34</v>
       </c>
       <c r="Z16">
-        <f>T16/W16</f>
+        <f t="shared" si="0"/>
         <v>6.4444444444444446</v>
       </c>
       <c r="AA16">
-        <f>Z16-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-0.99467618423564996</v>
       </c>
       <c r="AB16">
-        <f>R16-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-2.5253164556962027</v>
       </c>
       <c r="AC16">
-        <f>S16/(-110+17.25*Q16)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-28.313253012048193</v>
       </c>
       <c r="AD16">
-        <f>V16-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-1.924050632911392</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3279,7 +3289,7 @@
         <v>110</v>
       </c>
       <c r="K17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L17" t="s">
@@ -3322,27 +3332,27 @@
         <v>34</v>
       </c>
       <c r="Z17">
-        <f>T17/W17</f>
+        <f t="shared" si="0"/>
         <v>6.8108108108108105</v>
       </c>
       <c r="AA17">
-        <f>Z17-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-0.62830981786928408</v>
       </c>
       <c r="AB17">
-        <f>R17-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC17">
-        <f>S17/(-110+17.25*Q17)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-1.1406844106463865</v>
       </c>
       <c r="AD17">
-        <f>V17-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -3365,7 +3375,7 @@
         <v>149</v>
       </c>
       <c r="K18" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L18" t="s">
@@ -3408,27 +3418,27 @@
         <v>34</v>
       </c>
       <c r="Z18">
-        <f>T18/W18</f>
+        <f t="shared" si="0"/>
         <v>8.9655172413793096</v>
       </c>
       <c r="AA18">
-        <f>Z18-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>1.526396612699215</v>
       </c>
       <c r="AB18">
-        <f>R18-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC18">
-        <f>S18/(-110+17.25*Q18)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-4.1825095057034218</v>
       </c>
       <c r="AD18">
-        <f>V18-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>7</v>
       </c>
@@ -3454,7 +3464,7 @@
         <v>53</v>
       </c>
       <c r="K19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L19" t="s">
@@ -3497,27 +3507,27 @@
         <v>34</v>
       </c>
       <c r="Z19">
-        <f>T19/W19</f>
+        <f t="shared" si="0"/>
         <v>4.0975609756097562</v>
       </c>
       <c r="AA19">
-        <f>Z19-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-3.3415596530703384</v>
       </c>
       <c r="AB19">
-        <f>R19-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-2.5253164556962027</v>
       </c>
       <c r="AC19">
-        <f>S19/(-110+17.25*Q19)*100-100</f>
+        <f t="shared" si="3"/>
         <v>13.253012048192787</v>
       </c>
       <c r="AD19">
-        <f>V19-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>10</v>
       </c>
@@ -3540,7 +3550,7 @@
         <v>82</v>
       </c>
       <c r="K20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L20" t="s">
@@ -3583,27 +3593,27 @@
         <v>34</v>
       </c>
       <c r="Z20">
-        <f>T20/W20</f>
+        <f t="shared" si="0"/>
         <v>5.957446808510638</v>
       </c>
       <c r="AA20">
-        <f>Z20-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-1.4816738201694566</v>
       </c>
       <c r="AB20">
-        <f>R20-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-2.5316455696202667E-2</v>
       </c>
       <c r="AC20">
-        <f>S20/(-110+17.25*Q20)*100-100</f>
+        <f t="shared" si="3"/>
         <v>2.409638554216869</v>
       </c>
       <c r="AD20">
-        <f>V20-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-3.924050632911392</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>9</v>
       </c>
@@ -3626,7 +3636,7 @@
         <v>96</v>
       </c>
       <c r="K21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L21" t="s">
@@ -3669,27 +3679,27 @@
         <v>34</v>
       </c>
       <c r="Z21">
-        <f>T21/W21</f>
+        <f t="shared" si="0"/>
         <v>7.3684210526315788</v>
       </c>
       <c r="AA21">
-        <f>Z21-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-7.0699576048515844E-2</v>
       </c>
       <c r="AB21">
-        <f>R21-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-0.52531645569620267</v>
       </c>
       <c r="AC21">
-        <f>S21/(-110+17.25*Q21)*100-100</f>
+        <f t="shared" si="3"/>
         <v>25.361620057859227</v>
       </c>
       <c r="AD21">
-        <f>V21-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>11</v>
       </c>
@@ -3712,7 +3722,7 @@
         <v>117</v>
       </c>
       <c r="K22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L22" t="s">
@@ -3755,27 +3765,27 @@
         <v>34</v>
       </c>
       <c r="Z22">
-        <f>T22/W22</f>
+        <f t="shared" si="0"/>
         <v>7.5675675675675675</v>
       </c>
       <c r="AA22">
-        <f>Z22-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>0.12844693888747294</v>
       </c>
       <c r="AB22">
-        <f>R22-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-2.5316455696202667E-2</v>
       </c>
       <c r="AC22">
-        <f>S22/(-110+17.25*Q22)*100-100</f>
+        <f t="shared" si="3"/>
         <v>2.409638554216869</v>
       </c>
       <c r="AD22">
-        <f>V22-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>8</v>
       </c>
@@ -3798,7 +3808,7 @@
         <v>74</v>
       </c>
       <c r="K23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L23" t="s">
@@ -3841,27 +3851,27 @@
         <v>34</v>
       </c>
       <c r="Z23">
-        <f>T23/W23</f>
+        <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
       <c r="AA23">
-        <f>Z23-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-2.6391206286800948</v>
       </c>
       <c r="AB23">
-        <f>R23-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-2.5253164556962027</v>
       </c>
       <c r="AC23">
-        <f>S23/(-110+17.25*Q23)*100-100</f>
+        <f t="shared" si="3"/>
         <v>13.855421686746979</v>
       </c>
       <c r="AD23">
-        <f>V23-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>12</v>
       </c>
@@ -3884,7 +3894,7 @@
         <v>110</v>
       </c>
       <c r="K24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L24" t="s">
@@ -3927,27 +3937,27 @@
         <v>34</v>
       </c>
       <c r="Z24">
-        <f>T24/W24</f>
+        <f t="shared" si="0"/>
         <v>7.5675675675675675</v>
       </c>
       <c r="AA24">
-        <f>Z24-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>0.12844693888747294</v>
       </c>
       <c r="AB24">
-        <f>R24-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-2.5316455696202667E-2</v>
       </c>
       <c r="AC24">
-        <f>S24/(-110+17.25*Q24)*100-100</f>
+        <f t="shared" si="3"/>
         <v>2.409638554216869</v>
       </c>
       <c r="AD24">
-        <f>V24-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>15</v>
       </c>
@@ -3973,7 +3983,7 @@
         <v>160</v>
       </c>
       <c r="K25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L25" t="s">
@@ -4016,27 +4026,27 @@
         <v>34</v>
       </c>
       <c r="Z25">
-        <f>T25/W25</f>
+        <f t="shared" si="0"/>
         <v>9.931034482758621</v>
       </c>
       <c r="AA25">
-        <f>Z25-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>2.4919138540785264</v>
       </c>
       <c r="AB25">
-        <f>R25-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC25">
-        <f>S25/(-110+17.25*Q25)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-8.7452471482889678</v>
       </c>
       <c r="AD25">
-        <f>V25-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>16</v>
       </c>
@@ -4062,7 +4072,7 @@
         <v>160</v>
       </c>
       <c r="K26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L26" t="s">
@@ -4105,27 +4115,27 @@
         <v>34</v>
       </c>
       <c r="Z26">
-        <f>T26/W26</f>
+        <f t="shared" si="0"/>
         <v>9.931034482758621</v>
       </c>
       <c r="AA26">
-        <f>Z26-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>2.4919138540785264</v>
       </c>
       <c r="AB26">
-        <f>R26-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC26">
-        <f>S26/(-110+17.25*Q26)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-8.7452471482889678</v>
       </c>
       <c r="AD26">
-        <f>V26-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>13</v>
       </c>
@@ -4148,7 +4158,7 @@
         <v>131</v>
       </c>
       <c r="K27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L27" t="s">
@@ -4191,27 +4201,27 @@
         <v>34</v>
       </c>
       <c r="Z27">
-        <f>T27/W27</f>
+        <f t="shared" si="0"/>
         <v>8.1081081081081088</v>
       </c>
       <c r="AA27">
-        <f>Z27-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>0.66898747942801418</v>
       </c>
       <c r="AB27">
-        <f>R27-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC27">
-        <f>S27/(-110+17.25*Q27)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-2.6615969581749113</v>
       </c>
       <c r="AD27">
-        <f>V27-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>14</v>
       </c>
@@ -4234,7 +4244,7 @@
         <v>146</v>
       </c>
       <c r="K28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L28" t="s">
@@ -4277,27 +4287,27 @@
         <v>34</v>
       </c>
       <c r="Z28">
-        <f>T28/W28</f>
+        <f t="shared" si="0"/>
         <v>8.1081081081081088</v>
       </c>
       <c r="AA28">
-        <f>Z28-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>0.66898747942801418</v>
       </c>
       <c r="AB28">
-        <f>R28-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC28">
-        <f>S28/(-110+17.25*Q28)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-2.6615969581749113</v>
       </c>
       <c r="AD28">
-        <f>V28-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>17</v>
       </c>
@@ -4320,7 +4330,7 @@
         <v>203</v>
       </c>
       <c r="K29" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L29" t="s">
@@ -4363,27 +4373,27 @@
         <v>34</v>
       </c>
       <c r="Z29">
-        <f>T29/W29</f>
+        <f t="shared" si="0"/>
         <v>9.75</v>
       </c>
       <c r="AA29">
-        <f>Z29-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>2.3108793713199054</v>
       </c>
       <c r="AB29">
-        <f>R29-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC29">
-        <f>S29/(-110+17.25*Q29)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-9.6385542168674618</v>
       </c>
       <c r="AD29">
-        <f>V29-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>6</v>
       </c>
@@ -4406,7 +4416,7 @@
         <v>110</v>
       </c>
       <c r="K30" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L30" t="s">
@@ -4449,27 +4459,27 @@
         <v>34</v>
       </c>
       <c r="Z30">
-        <f>T30/W30</f>
+        <f t="shared" si="0"/>
         <v>8.7272727272727266</v>
       </c>
       <c r="AA30">
-        <f>Z30-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>1.288152098592632</v>
       </c>
       <c r="AB30">
-        <f>R30-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-0.52531645569620267</v>
       </c>
       <c r="AC30">
-        <f>S30/(-110+17.25*Q30)*100-100</f>
+        <f t="shared" si="3"/>
         <v>-31.55893536121674</v>
       </c>
       <c r="AD30">
-        <f>V30-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>23</v>
       </c>
@@ -4492,7 +4502,7 @@
         <v>45</v>
       </c>
       <c r="K31" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L31" t="s">
@@ -4535,27 +4545,27 @@
         <v>34</v>
       </c>
       <c r="Z31">
-        <f>T31/W31</f>
+        <f t="shared" si="0"/>
         <v>4.3157894736842106</v>
       </c>
       <c r="AA31">
-        <f>Z31-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-3.123331154995884</v>
       </c>
       <c r="AB31">
-        <f>R31-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-3.5253164556962027</v>
       </c>
       <c r="AC31">
-        <f>S31/(-110+17.25*Q31)*100-100</f>
+        <f t="shared" si="3"/>
         <v>6.4638783269961948</v>
       </c>
       <c r="AD31">
-        <f>V31-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>19</v>
       </c>
@@ -4581,7 +4591,7 @@
         <v>45</v>
       </c>
       <c r="K32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L32" t="s">
@@ -4624,27 +4634,27 @@
         <v>34</v>
       </c>
       <c r="Z32">
-        <f>T32/W32</f>
+        <f t="shared" si="0"/>
         <v>4.3157894736842106</v>
       </c>
       <c r="AA32">
-        <f>Z32-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-3.123331154995884</v>
       </c>
       <c r="AB32">
-        <f>R32-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-3.5253164556962027</v>
       </c>
       <c r="AC32">
-        <f>S32/(-110+17.25*Q32)*100-100</f>
+        <f t="shared" si="3"/>
         <v>6.4638783269961948</v>
       </c>
       <c r="AD32">
-        <f>V32-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>25</v>
       </c>
@@ -4667,7 +4677,7 @@
         <v>78</v>
       </c>
       <c r="K33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L33" t="s">
@@ -4710,27 +4720,27 @@
         <v>34</v>
       </c>
       <c r="Z33">
-        <f>T33/W33</f>
+        <f t="shared" si="0"/>
         <v>4.9142857142857146</v>
       </c>
       <c r="AA33">
-        <f>Z33-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="1"/>
         <v>-2.52483491439438</v>
       </c>
       <c r="AB33">
-        <f>R33-AVERAGE(R:R)</f>
+        <f t="shared" si="2"/>
         <v>-2.5253164556962027</v>
       </c>
       <c r="AC33">
-        <f>S33/(-110+17.25*Q33)*100-100</f>
+        <f t="shared" si="3"/>
         <v>7.8313253012048278</v>
       </c>
       <c r="AD33">
-        <f>V33-AVERAGE(V:V)</f>
+        <f t="shared" si="4"/>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>27</v>
       </c>
@@ -4750,10 +4760,10 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L34" t="s">
@@ -4796,27 +4806,27 @@
         <v>34</v>
       </c>
       <c r="Z34">
-        <f>T34/W34</f>
+        <f t="shared" ref="Z34:Z65" si="6">T34/W34</f>
         <v>6.3783783783783781</v>
       </c>
       <c r="AA34">
-        <f>Z34-(AVERAGE(Z:Z))</f>
+        <f t="shared" ref="AA34:AA65" si="7">Z34-(AVERAGE(Z:Z))</f>
         <v>-1.0607422503017165</v>
       </c>
       <c r="AB34">
-        <f>R34-AVERAGE(R:R)</f>
+        <f t="shared" ref="AB34:AB65" si="8">R34-AVERAGE(R:R)</f>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC34">
-        <f>S34/(-110+17.25*Q34)*100-100</f>
+        <f t="shared" ref="AC34:AC65" si="9">S34/(-110+17.25*Q34)*100-100</f>
         <v>7.2243346007604572</v>
       </c>
       <c r="AD34">
-        <f>V34-AVERAGE(V:V)</f>
+        <f t="shared" ref="AD34:AD65" si="10">V34-AVERAGE(V:V)</f>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>20</v>
       </c>
@@ -4842,7 +4852,7 @@
         <v>47</v>
       </c>
       <c r="K35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L35" t="s">
@@ -4885,27 +4895,27 @@
         <v>34</v>
       </c>
       <c r="Z35">
-        <f>T35/W35</f>
+        <f t="shared" si="6"/>
         <v>4.2051282051282053</v>
       </c>
       <c r="AA35">
-        <f>Z35-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-3.2339924235518893</v>
       </c>
       <c r="AB35">
-        <f>R35-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-3.5253164556962027</v>
       </c>
       <c r="AC35">
-        <f>S35/(-110+17.25*Q35)*100-100</f>
+        <f t="shared" si="9"/>
         <v>-6.285355122562919E-2</v>
       </c>
       <c r="AD35">
-        <f>V35-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>21</v>
       </c>
@@ -4928,7 +4938,7 @@
         <v>50</v>
       </c>
       <c r="K36" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L36" t="s">
@@ -4971,27 +4981,27 @@
         <v>34</v>
       </c>
       <c r="Z36">
-        <f>T36/W36</f>
+        <f t="shared" si="6"/>
         <v>4.5555555555555554</v>
       </c>
       <c r="AA36">
-        <f>Z36-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-2.8835650731245392</v>
       </c>
       <c r="AB36">
-        <f>R36-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-4.5253164556962027</v>
       </c>
       <c r="AC36">
-        <f>S36/(-110+17.25*Q36)*100-100</f>
+        <f t="shared" si="9"/>
         <v>-4.4626021370207241</v>
       </c>
       <c r="AD36">
-        <f>V36-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>24</v>
       </c>
@@ -5014,7 +5024,7 @@
         <v>72</v>
       </c>
       <c r="K37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L37" t="s">
@@ -5057,27 +5067,27 @@
         <v>34</v>
       </c>
       <c r="Z37">
-        <f>T37/W37</f>
+        <f t="shared" si="6"/>
         <v>4.6857142857142859</v>
       </c>
       <c r="AA37">
-        <f>Z37-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-2.7534063429658087</v>
       </c>
       <c r="AB37">
-        <f>R37-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-3.5253164556962027</v>
       </c>
       <c r="AC37">
-        <f>S37/(-110+17.25*Q37)*100-100</f>
+        <f t="shared" si="9"/>
         <v>6.8510370835952443</v>
       </c>
       <c r="AD37">
-        <f>V37-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>26</v>
       </c>
@@ -5100,7 +5110,7 @@
         <v>133</v>
       </c>
       <c r="K38" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L38" t="s">
@@ -5143,27 +5153,27 @@
         <v>34</v>
       </c>
       <c r="Z38">
-        <f>T38/W38</f>
+        <f t="shared" si="6"/>
         <v>5.375</v>
       </c>
       <c r="AA38">
-        <f>Z38-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-2.0641206286800946</v>
       </c>
       <c r="AB38">
-        <f>R38-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-0.52531645569620267</v>
       </c>
       <c r="AC38">
-        <f>S38/(-110+17.25*Q38)*100-100</f>
+        <f t="shared" si="9"/>
         <v>-13.347921225382933</v>
       </c>
       <c r="AD38">
-        <f>V38-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>28</v>
       </c>
@@ -5186,7 +5196,7 @@
         <v>107</v>
       </c>
       <c r="K39" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L39" t="s">
@@ -5229,27 +5239,27 @@
         <v>34</v>
       </c>
       <c r="Z39">
-        <f>T39/W39</f>
+        <f t="shared" si="6"/>
         <v>9.8333333333333339</v>
       </c>
       <c r="AA39">
-        <f>Z39-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>2.3942127046532393</v>
       </c>
       <c r="AB39">
-        <f>R39-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-2.5253164556962027</v>
       </c>
       <c r="AC39">
-        <f>S39/(-110+17.25*Q39)*100-100</f>
+        <f t="shared" si="9"/>
         <v>5.7034220532319324</v>
       </c>
       <c r="AD39">
-        <f>V39-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>29</v>
       </c>
@@ -5272,7 +5282,7 @@
         <v>139</v>
       </c>
       <c r="K40" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L40" t="s">
@@ -5315,27 +5325,27 @@
         <v>34</v>
       </c>
       <c r="Z40">
-        <f>T40/W40</f>
+        <f t="shared" si="6"/>
         <v>8.137931034482758</v>
       </c>
       <c r="AA40">
-        <f>Z40-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>0.6988104058026634</v>
       </c>
       <c r="AB40">
-        <f>R40-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC40">
-        <f>S40/(-110+17.25*Q40)*100-100</f>
+        <f t="shared" si="9"/>
         <v>5.7034220532319324</v>
       </c>
       <c r="AD40">
-        <f>V40-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>31</v>
       </c>
@@ -5358,7 +5368,7 @@
         <v>176</v>
       </c>
       <c r="K41" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L41" t="s">
@@ -5401,27 +5411,27 @@
         <v>34</v>
       </c>
       <c r="Z41">
-        <f>T41/W41</f>
+        <f t="shared" si="6"/>
         <v>8.8275862068965516</v>
       </c>
       <c r="AA41">
-        <f>Z41-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>1.388465578216457</v>
       </c>
       <c r="AB41">
-        <f>R41-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC41">
-        <f>S41/(-110+17.25*Q41)*100-100</f>
+        <f t="shared" si="9"/>
         <v>2.6615969581748971</v>
       </c>
       <c r="AD41">
-        <f>V41-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>22</v>
       </c>
@@ -5444,7 +5454,7 @@
         <v>210</v>
       </c>
       <c r="K42" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L42" t="s">
@@ -5487,27 +5497,27 @@
         <v>34</v>
       </c>
       <c r="Z42">
-        <f>T42/W42</f>
+        <f t="shared" si="6"/>
         <v>9.481481481481481</v>
       </c>
       <c r="AA42">
-        <f>Z42-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>2.0423608528013864</v>
       </c>
       <c r="AB42">
-        <f>R42-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC42">
-        <f>S42/(-110+17.25*Q42)*100-100</f>
+        <f t="shared" si="9"/>
         <v>-9.5057034220532302</v>
       </c>
       <c r="AD42">
-        <f>V42-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>30</v>
       </c>
@@ -5530,7 +5540,7 @@
         <v>160</v>
       </c>
       <c r="K43" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L43" t="s">
@@ -5573,27 +5583,27 @@
         <v>34</v>
       </c>
       <c r="Z43">
-        <f>T43/W43</f>
+        <f t="shared" si="6"/>
         <v>8.137931034482758</v>
       </c>
       <c r="AA43">
-        <f>Z43-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>0.6988104058026634</v>
       </c>
       <c r="AB43">
-        <f>R43-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC43">
-        <f>S43/(-110+17.25*Q43)*100-100</f>
+        <f t="shared" si="9"/>
         <v>5.7034220532319324</v>
       </c>
       <c r="AD43">
-        <f>V43-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>32</v>
       </c>
@@ -5616,7 +5626,7 @@
         <v>203</v>
       </c>
       <c r="K44" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L44" t="s">
@@ -5659,27 +5669,27 @@
         <v>34</v>
       </c>
       <c r="Z44">
-        <f>T44/W44</f>
+        <f t="shared" si="6"/>
         <v>8.8275862068965516</v>
       </c>
       <c r="AA44">
-        <f>Z44-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>1.388465578216457</v>
       </c>
       <c r="AB44">
-        <f>R44-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC44">
-        <f>S44/(-110+17.25*Q44)*100-100</f>
+        <f t="shared" si="9"/>
         <v>2.6615969581748971</v>
       </c>
       <c r="AD44">
-        <f>V44-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5699,10 +5709,10 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K45" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L45" t="s">
@@ -5745,27 +5755,27 @@
         <v>34</v>
       </c>
       <c r="Z45">
-        <f>T45/W45</f>
+        <f t="shared" si="6"/>
         <v>4.3902439024390247</v>
       </c>
       <c r="AA45">
-        <f>Z45-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-3.0488767262410699</v>
       </c>
       <c r="AB45">
-        <f>R45-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-3.5253164556962027</v>
       </c>
       <c r="AC45">
-        <f>S45/(-110+17.25*Q45)*100-100</f>
+        <f t="shared" si="9"/>
         <v>1.8227529855437012</v>
       </c>
       <c r="AD45">
-        <f>V45-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>34</v>
       </c>
@@ -5788,7 +5798,7 @@
         <v>56</v>
       </c>
       <c r="K46" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L46" t="s">
@@ -5831,27 +5841,27 @@
         <v>34</v>
       </c>
       <c r="Z46">
-        <f>T46/W46</f>
+        <f t="shared" si="6"/>
         <v>4.4761904761904763</v>
       </c>
       <c r="AA46">
-        <f>Z46-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-2.9629301524896183</v>
       </c>
       <c r="AB46">
-        <f>R46-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-3.5253164556962027</v>
       </c>
       <c r="AC46">
-        <f>S46/(-110+17.25*Q46)*100-100</f>
+        <f t="shared" si="9"/>
         <v>1.1942174732872672</v>
       </c>
       <c r="AD46">
-        <f>V46-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-3.924050632911392</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>33</v>
       </c>
@@ -5874,7 +5884,7 @@
         <v>39</v>
       </c>
       <c r="K47" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L47" t="s">
@@ -5917,27 +5927,27 @@
         <v>34</v>
       </c>
       <c r="Z47">
-        <f>T47/W47</f>
+        <f t="shared" si="6"/>
         <v>4.177777777777778</v>
       </c>
       <c r="AA47">
-        <f>Z47-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-3.2613428509023166</v>
       </c>
       <c r="AB47">
-        <f>R47-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-3.5253164556962027</v>
       </c>
       <c r="AC47">
-        <f>S47/(-110+17.25*Q47)*100-100</f>
+        <f t="shared" si="9"/>
         <v>2.4512884978001352</v>
       </c>
       <c r="AD47">
-        <f>V47-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-4.924050632911392</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>45</v>
       </c>
@@ -5960,7 +5970,7 @@
         <v>112</v>
       </c>
       <c r="K48" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L48" t="s">
@@ -6003,27 +6013,27 @@
         <v>34</v>
       </c>
       <c r="Z48">
-        <f>T48/W48</f>
+        <f t="shared" si="6"/>
         <v>7.0588235294117645</v>
       </c>
       <c r="AA48">
-        <f>Z48-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-0.38029709926833011</v>
       </c>
       <c r="AB48">
-        <f>R48-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-2.5316455696202667E-2</v>
       </c>
       <c r="AC48">
-        <f>S48/(-110+17.25*Q48)*100-100</f>
+        <f t="shared" si="9"/>
         <v>5.7034220532319324</v>
       </c>
       <c r="AD48">
-        <f>V48-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6046,7 +6056,7 @@
         <v>120</v>
       </c>
       <c r="K49" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L49" t="s">
@@ -6089,27 +6099,27 @@
         <v>34</v>
       </c>
       <c r="Z49">
-        <f>T49/W49</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="AA49">
-        <f>Z49-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-1.4391206286800946</v>
       </c>
       <c r="AB49">
-        <f>R49-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC49">
-        <f>S49/(-110+17.25*Q49)*100-100</f>
+        <f t="shared" si="9"/>
         <v>1.8072289156626482</v>
       </c>
       <c r="AD49">
-        <f>V49-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>46</v>
       </c>
@@ -6132,7 +6142,7 @@
         <v>126</v>
       </c>
       <c r="K50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L50" t="s">
@@ -6175,27 +6185,27 @@
         <v>34</v>
       </c>
       <c r="Z50">
-        <f>T50/W50</f>
+        <f t="shared" si="6"/>
         <v>7.0588235294117645</v>
       </c>
       <c r="AA50">
-        <f>Z50-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-0.38029709926833011</v>
       </c>
       <c r="AB50">
-        <f>R50-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-2.5316455696202667E-2</v>
       </c>
       <c r="AC50">
-        <f>S50/(-110+17.25*Q50)*100-100</f>
+        <f t="shared" si="9"/>
         <v>5.7034220532319324</v>
       </c>
       <c r="AD50">
-        <f>V50-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>52</v>
       </c>
@@ -6218,7 +6228,7 @@
         <v>133</v>
       </c>
       <c r="K51" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L51" t="s">
@@ -6261,27 +6271,27 @@
         <v>34</v>
       </c>
       <c r="Z51">
-        <f>T51/W51</f>
+        <f t="shared" si="6"/>
         <v>5.7</v>
       </c>
       <c r="AA51">
-        <f>Z51-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-1.7391206286800944</v>
       </c>
       <c r="AB51">
-        <f>R51-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>0.47468354430379733</v>
       </c>
       <c r="AC51">
-        <f>S51/(-110+17.25*Q51)*100-100</f>
+        <f t="shared" si="9"/>
         <v>14.457831325301214</v>
       </c>
       <c r="AD51">
-        <f>V51-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>43</v>
       </c>
@@ -6307,7 +6317,7 @@
         <v>72</v>
       </c>
       <c r="K52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L52" t="s">
@@ -6350,27 +6360,27 @@
         <v>34</v>
       </c>
       <c r="Z52">
-        <f>T52/W52</f>
+        <f t="shared" si="6"/>
         <v>5.2173913043478262</v>
       </c>
       <c r="AA52">
-        <f>Z52-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-2.2217293243322684</v>
       </c>
       <c r="AB52">
-        <f>R52-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC52">
-        <f>S52/(-110+17.25*Q52)*100-100</f>
+        <f t="shared" si="9"/>
         <v>0.34889516530986953</v>
       </c>
       <c r="AD52">
-        <f>V52-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>35</v>
       </c>
@@ -6393,7 +6403,7 @@
         <v>64</v>
       </c>
       <c r="K53" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L53" t="s">
@@ -6436,27 +6446,27 @@
         <v>34</v>
       </c>
       <c r="Z53">
-        <f>T53/W53</f>
+        <f t="shared" si="6"/>
         <v>6.3157894736842106</v>
       </c>
       <c r="AA53">
-        <f>Z53-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-1.123331154995884</v>
       </c>
       <c r="AB53">
-        <f>R53-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-0.52531645569620267</v>
       </c>
       <c r="AC53">
-        <f>S53/(-110+17.25*Q53)*100-100</f>
+        <f t="shared" si="9"/>
         <v>14.068441064638776</v>
       </c>
       <c r="AD53">
-        <f>V53-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>37</v>
       </c>
@@ -6479,7 +6489,7 @@
         <v>69</v>
       </c>
       <c r="K54" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L54" t="s">
@@ -6522,27 +6532,27 @@
         <v>34</v>
       </c>
       <c r="Z54">
-        <f>T54/W54</f>
+        <f t="shared" si="6"/>
         <v>6.8292682926829267</v>
       </c>
       <c r="AA54">
-        <f>Z54-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-0.60985233599716793</v>
       </c>
       <c r="AB54">
-        <f>R54-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-0.52531645569620267</v>
       </c>
       <c r="AC54">
-        <f>S54/(-110+17.25*Q54)*100-100</f>
+        <f t="shared" si="9"/>
         <v>8.4337349397590344</v>
       </c>
       <c r="AD54">
-        <f>V54-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>40</v>
       </c>
@@ -6568,7 +6578,7 @@
         <v>69</v>
       </c>
       <c r="K55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L55" t="s">
@@ -6611,27 +6621,27 @@
         <v>34</v>
       </c>
       <c r="Z55">
-        <f>T55/W55</f>
+        <f t="shared" si="6"/>
         <v>6.4864864864864868</v>
       </c>
       <c r="AA55">
-        <f>Z55-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-0.95263414219360776</v>
       </c>
       <c r="AB55">
-        <f>R55-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-2.5316455696202667E-2</v>
       </c>
       <c r="AC55">
-        <f>S55/(-110+17.25*Q55)*100-100</f>
+        <f t="shared" si="9"/>
         <v>1.1406844106463865</v>
       </c>
       <c r="AD55">
-        <f>V55-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>7.5949367088608E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>41</v>
       </c>
@@ -6657,7 +6667,7 @@
         <v>80</v>
       </c>
       <c r="K56" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L56" t="s">
@@ -6700,27 +6710,27 @@
         <v>34</v>
       </c>
       <c r="Z56">
-        <f>T56/W56</f>
+        <f t="shared" si="6"/>
         <v>5.5813953488372094</v>
       </c>
       <c r="AA56">
-        <f>Z56-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-1.8577252798428852</v>
       </c>
       <c r="AB56">
-        <f>R56-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC56">
-        <f>S56/(-110+17.25*Q56)*100-100</f>
+        <f t="shared" si="9"/>
         <v>0.34889516530986953</v>
       </c>
       <c r="AD56">
-        <f>V56-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>7.5949367088608E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>42</v>
       </c>
@@ -6746,7 +6756,7 @@
         <v>69</v>
       </c>
       <c r="K57" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L57" t="s">
@@ -6789,27 +6799,27 @@
         <v>34</v>
       </c>
       <c r="Z57">
-        <f>T57/W57</f>
+        <f t="shared" si="6"/>
         <v>5.8536585365853657</v>
       </c>
       <c r="AA57">
-        <f>Z57-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-1.5854620920947289</v>
       </c>
       <c r="AB57">
-        <f>R57-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-2.5253164556962027</v>
       </c>
       <c r="AC57">
-        <f>S57/(-110+17.25*Q57)*100-100</f>
+        <f t="shared" si="9"/>
         <v>5.895728439174917</v>
       </c>
       <c r="AD57">
-        <f>V57-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>7.5949367088608E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>49</v>
       </c>
@@ -6832,7 +6842,7 @@
         <v>125</v>
       </c>
       <c r="K58" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L58" t="s">
@@ -6875,27 +6885,27 @@
         <v>34</v>
       </c>
       <c r="Z58">
-        <f>T58/W58</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="AA58">
-        <f>Z58-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-1.4391206286800946</v>
       </c>
       <c r="AB58">
-        <f>R58-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC58">
-        <f>S58/(-110+17.25*Q58)*100-100</f>
+        <f t="shared" si="9"/>
         <v>1.8072289156626482</v>
       </c>
       <c r="AD58">
-        <f>V58-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>36</v>
       </c>
@@ -6918,7 +6928,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L59" t="s">
@@ -6961,27 +6971,27 @@
         <v>34</v>
       </c>
       <c r="Z59">
-        <f>T59/W59</f>
+        <f t="shared" si="6"/>
         <v>6.3157894736842106</v>
       </c>
       <c r="AA59">
-        <f>Z59-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-1.123331154995884</v>
       </c>
       <c r="AB59">
-        <f>R59-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-0.52531645569620267</v>
       </c>
       <c r="AC59">
-        <f>S59/(-110+17.25*Q59)*100-100</f>
+        <f t="shared" si="9"/>
         <v>14.068441064638776</v>
       </c>
       <c r="AD59">
-        <f>V59-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>38</v>
       </c>
@@ -7004,7 +7014,7 @@
         <v>80</v>
       </c>
       <c r="K60" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L60" t="s">
@@ -7047,27 +7057,27 @@
         <v>34</v>
       </c>
       <c r="Z60">
-        <f>T60/W60</f>
+        <f t="shared" si="6"/>
         <v>6.8292682926829267</v>
       </c>
       <c r="AA60">
-        <f>Z60-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-0.60985233599716793</v>
       </c>
       <c r="AB60">
-        <f>R60-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-0.52531645569620267</v>
       </c>
       <c r="AC60">
-        <f>S60/(-110+17.25*Q60)*100-100</f>
+        <f t="shared" si="9"/>
         <v>8.4337349397590344</v>
       </c>
       <c r="AD60">
-        <f>V60-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>39</v>
       </c>
@@ -7090,7 +7100,7 @@
         <v>123</v>
       </c>
       <c r="K61" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L61" t="s">
@@ -7133,27 +7143,27 @@
         <v>34</v>
       </c>
       <c r="Z61">
-        <f>T61/W61</f>
+        <f t="shared" si="6"/>
         <v>7.4736842105263159</v>
       </c>
       <c r="AA61">
-        <f>Z61-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>3.4563581846221325E-2</v>
       </c>
       <c r="AB61">
-        <f>R61-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>0.47468354430379733</v>
       </c>
       <c r="AC61">
-        <f>S61/(-110+17.25*Q61)*100-100</f>
+        <f t="shared" si="9"/>
         <v>8.4337349397590344</v>
       </c>
       <c r="AD61">
-        <f>V61-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>47</v>
       </c>
@@ -7176,7 +7186,7 @@
         <v>107</v>
       </c>
       <c r="K62" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L62" t="s">
@@ -7219,27 +7229,27 @@
         <v>34</v>
       </c>
       <c r="Z62">
-        <f>T62/W62</f>
+        <f t="shared" si="6"/>
         <v>7.0588235294117645</v>
       </c>
       <c r="AA62">
-        <f>Z62-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-0.38029709926833011</v>
       </c>
       <c r="AB62">
-        <f>R62-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>-2.5316455696202667E-2</v>
       </c>
       <c r="AC62">
-        <f>S62/(-110+17.25*Q62)*100-100</f>
+        <f t="shared" si="9"/>
         <v>5.7034220532319324</v>
       </c>
       <c r="AD62">
-        <f>V62-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>50</v>
       </c>
@@ -7262,7 +7272,7 @@
         <v>115</v>
       </c>
       <c r="K63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L63" t="s">
@@ -7305,27 +7315,27 @@
         <v>34</v>
       </c>
       <c r="Z63">
-        <f>T63/W63</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="AA63">
-        <f>Z63-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>-1.4391206286800946</v>
       </c>
       <c r="AB63">
-        <f>R63-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC63">
-        <f>S63/(-110+17.25*Q63)*100-100</f>
+        <f t="shared" si="9"/>
         <v>1.8072289156626482</v>
       </c>
       <c r="AD63">
-        <f>V63-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>53</v>
       </c>
@@ -7351,7 +7361,7 @@
         <v>160</v>
       </c>
       <c r="K64" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L64" t="s">
@@ -7394,27 +7404,27 @@
         <v>34</v>
       </c>
       <c r="Z64">
-        <f>T64/W64</f>
+        <f t="shared" si="6"/>
         <v>9.6551724137931032</v>
       </c>
       <c r="AA64">
-        <f>Z64-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>2.2160517851130086</v>
       </c>
       <c r="AB64">
-        <f>R64-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC64">
-        <f>S64/(-110+17.25*Q64)*100-100</f>
+        <f t="shared" si="9"/>
         <v>4.9429657794676842</v>
       </c>
       <c r="AD64">
-        <f>V64-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>54</v>
       </c>
@@ -7440,7 +7450,7 @@
         <v>168</v>
       </c>
       <c r="K65" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L65" t="s">
@@ -7483,27 +7493,27 @@
         <v>34</v>
       </c>
       <c r="Z65">
-        <f>T65/W65</f>
+        <f t="shared" si="6"/>
         <v>9.6551724137931032</v>
       </c>
       <c r="AA65">
-        <f>Z65-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="7"/>
         <v>2.2160517851130086</v>
       </c>
       <c r="AB65">
-        <f>R65-AVERAGE(R:R)</f>
+        <f t="shared" si="8"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC65">
-        <f>S65/(-110+17.25*Q65)*100-100</f>
+        <f t="shared" si="9"/>
         <v>4.9429657794676842</v>
       </c>
       <c r="AD65">
-        <f>V65-AVERAGE(V:V)</f>
+        <f t="shared" si="10"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>57</v>
       </c>
@@ -7526,7 +7536,7 @@
         <v>165</v>
       </c>
       <c r="K66" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="L66" t="s">
@@ -7569,27 +7579,27 @@
         <v>34</v>
       </c>
       <c r="Z66">
-        <f>T66/W66</f>
+        <f t="shared" ref="Z66:Z80" si="11">T66/W66</f>
         <v>9.6551724137931032</v>
       </c>
       <c r="AA66">
-        <f>Z66-(AVERAGE(Z:Z))</f>
+        <f t="shared" ref="AA66:AA97" si="12">Z66-(AVERAGE(Z:Z))</f>
         <v>2.2160517851130086</v>
       </c>
       <c r="AB66">
-        <f>R66-AVERAGE(R:R)</f>
+        <f t="shared" ref="AB66:AB80" si="13">R66-AVERAGE(R:R)</f>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC66">
-        <f>S66/(-110+17.25*Q66)*100-100</f>
+        <f t="shared" ref="AC66:AC80" si="14">S66/(-110+17.25*Q66)*100-100</f>
         <v>-9.5057034220532302</v>
       </c>
       <c r="AD66">
-        <f>V66-AVERAGE(V:V)</f>
+        <f t="shared" ref="AD66:AD80" si="15">V66-AVERAGE(V:V)</f>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>55</v>
       </c>
@@ -7615,7 +7625,7 @@
         <v>170</v>
       </c>
       <c r="K67" t="str">
-        <f t="shared" ref="K67:K80" si="1">IF(X67&lt;&gt;"쿠팡", ((J67-I67)/I67)*100, "")</f>
+        <f t="shared" ref="K67:K80" si="16">IF(X67&lt;&gt;"쿠팡", ((J67-I67)/I67)*100, "")</f>
         <v/>
       </c>
       <c r="L67" t="s">
@@ -7658,27 +7668,27 @@
         <v>34</v>
       </c>
       <c r="Z67">
-        <f>T67/W67</f>
+        <f t="shared" si="11"/>
         <v>9.6551724137931032</v>
       </c>
       <c r="AA67">
-        <f>Z67-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>2.2160517851130086</v>
       </c>
       <c r="AB67">
-        <f>R67-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC67">
-        <f>S67/(-110+17.25*Q67)*100-100</f>
+        <f t="shared" si="14"/>
         <v>4.9429657794676842</v>
       </c>
       <c r="AD67">
-        <f>V67-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>56</v>
       </c>
@@ -7704,7 +7714,7 @@
         <v>178</v>
       </c>
       <c r="K68" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L68" t="s">
@@ -7747,27 +7757,27 @@
         <v>34</v>
       </c>
       <c r="Z68">
-        <f>T68/W68</f>
+        <f t="shared" si="11"/>
         <v>9.6551724137931032</v>
       </c>
       <c r="AA68">
-        <f>Z68-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>2.2160517851130086</v>
       </c>
       <c r="AB68">
-        <f>R68-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC68">
-        <f>S68/(-110+17.25*Q68)*100-100</f>
+        <f t="shared" si="14"/>
         <v>4.9429657794676842</v>
       </c>
       <c r="AD68">
-        <f>V68-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>60</v>
       </c>
@@ -7787,10 +7797,10 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="K69" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L69" t="s">
@@ -7833,27 +7843,27 @@
         <v>34</v>
       </c>
       <c r="Z69">
-        <f>T69/W69</f>
+        <f t="shared" si="11"/>
         <v>8.4210526315789469</v>
       </c>
       <c r="AA69">
-        <f>Z69-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>0.9819320028988523</v>
       </c>
       <c r="AB69">
-        <f>R69-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC69">
-        <f>S69/(-110+17.25*Q69)*100-100</f>
+        <f t="shared" si="14"/>
         <v>12.204312329914174</v>
       </c>
       <c r="AD69">
-        <f>V69-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>-1.924050632911392</v>
       </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>51</v>
       </c>
@@ -7876,7 +7886,7 @@
         <v>125</v>
       </c>
       <c r="K70" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L70" t="s">
@@ -7919,27 +7929,27 @@
         <v>34</v>
       </c>
       <c r="Z70">
-        <f>T70/W70</f>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="AA70">
-        <f>Z70-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>-1.4391206286800946</v>
       </c>
       <c r="AB70">
-        <f>R70-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC70">
-        <f>S70/(-110+17.25*Q70)*100-100</f>
+        <f t="shared" si="14"/>
         <v>1.8072289156626482</v>
       </c>
       <c r="AD70">
-        <f>V70-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>58</v>
       </c>
@@ -7962,7 +7972,7 @@
         <v>176</v>
       </c>
       <c r="K71" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L71" t="s">
@@ -8005,27 +8015,27 @@
         <v>34</v>
       </c>
       <c r="Z71">
-        <f>T71/W71</f>
+        <f t="shared" si="11"/>
         <v>9.6551724137931032</v>
       </c>
       <c r="AA71">
-        <f>Z71-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>2.2160517851130086</v>
       </c>
       <c r="AB71">
-        <f>R71-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>1.4746835443037973</v>
       </c>
       <c r="AC71">
-        <f>S71/(-110+17.25*Q71)*100-100</f>
+        <f t="shared" si="14"/>
         <v>-9.5057034220532302</v>
       </c>
       <c r="AD71">
-        <f>V71-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>59</v>
       </c>
@@ -8048,7 +8058,7 @@
         <v>187</v>
       </c>
       <c r="K72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L72" t="s">
@@ -8091,27 +8101,27 @@
         <v>34</v>
       </c>
       <c r="Z72">
-        <f>T72/W72</f>
+        <f t="shared" si="11"/>
         <v>9.3333333333333339</v>
       </c>
       <c r="AA72">
-        <f>Z72-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>1.8942127046532393</v>
       </c>
       <c r="AB72">
-        <f>R72-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>0.97468354430379733</v>
       </c>
       <c r="AC72">
-        <f>S72/(-110+17.25*Q72)*100-100</f>
+        <f t="shared" si="14"/>
         <v>-0.6009420172161839</v>
       </c>
       <c r="AD72">
-        <f>V72-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>68</v>
       </c>
@@ -8134,7 +8144,7 @@
         <v>139</v>
       </c>
       <c r="K73" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L73" t="s">
@@ -8177,27 +8187,27 @@
         <v>34</v>
       </c>
       <c r="Z73">
-        <f>T73/W73</f>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="AA73">
-        <f>Z73-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>1.5608793713199054</v>
       </c>
       <c r="AB73">
-        <f>R73-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>-0.52531645569620267</v>
       </c>
       <c r="AC73">
-        <f>S73/(-110+17.25*Q73)*100-100</f>
+        <f t="shared" si="14"/>
         <v>-14.828897338403053</v>
       </c>
       <c r="AD73">
-        <f>V73-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>69</v>
       </c>
@@ -8220,7 +8230,7 @@
         <v>176</v>
       </c>
       <c r="K74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L74" t="s">
@@ -8263,27 +8273,27 @@
         <v>34</v>
       </c>
       <c r="Z74">
-        <f>T74/W74</f>
+        <f t="shared" si="11"/>
         <v>8.1052631578947363</v>
       </c>
       <c r="AA74">
-        <f>Z74-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>0.66614252921464168</v>
       </c>
       <c r="AB74">
-        <f>R74-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>0.97468354430379733</v>
       </c>
       <c r="AC74">
-        <f>S74/(-110+17.25*Q74)*100-100</f>
+        <f t="shared" si="14"/>
         <v>-27.710843373493972</v>
       </c>
       <c r="AD74">
-        <f>V74-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>72</v>
       </c>
@@ -8306,7 +8316,7 @@
         <v>187</v>
       </c>
       <c r="K75" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L75" t="s">
@@ -8349,27 +8359,27 @@
         <v>34</v>
       </c>
       <c r="Z75">
-        <f>T75/W75</f>
+        <f t="shared" si="11"/>
         <v>8.1052631578947363</v>
       </c>
       <c r="AA75">
-        <f>Z75-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>0.66614252921464168</v>
       </c>
       <c r="AB75">
-        <f>R75-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>0.97468354430379733</v>
       </c>
       <c r="AC75">
-        <f>S75/(-110+17.25*Q75)*100-100</f>
+        <f t="shared" si="14"/>
         <v>-24.147339699863579</v>
       </c>
       <c r="AD75">
-        <f>V75-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>73</v>
       </c>
@@ -8392,7 +8402,7 @@
         <v>176</v>
       </c>
       <c r="K76" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L76" t="s">
@@ -8435,27 +8445,27 @@
         <v>34</v>
       </c>
       <c r="Z76">
-        <f>T76/W76</f>
+        <f t="shared" si="11"/>
         <v>8.1052631578947363</v>
       </c>
       <c r="AA76">
-        <f>Z76-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>0.66614252921464168</v>
       </c>
       <c r="AB76">
-        <f>R76-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>0.97468354430379733</v>
       </c>
       <c r="AC76">
-        <f>S76/(-110+17.25*Q76)*100-100</f>
+        <f t="shared" si="14"/>
         <v>-15.662650602409627</v>
       </c>
       <c r="AD76">
-        <f>V76-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>70</v>
       </c>
@@ -8481,7 +8491,7 @@
         <v>181</v>
       </c>
       <c r="K77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L77" t="s">
@@ -8524,27 +8534,27 @@
         <v>34</v>
       </c>
       <c r="Z77">
-        <f>T77/W77</f>
+        <f t="shared" si="11"/>
         <v>10.266666666666667</v>
       </c>
       <c r="AA77">
-        <f>Z77-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>2.8275460379865729</v>
       </c>
       <c r="AB77">
-        <f>R77-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>0.97468354430379733</v>
       </c>
       <c r="AC77">
-        <f>S77/(-110+17.25*Q77)*100-100</f>
+        <f t="shared" si="14"/>
         <v>-27.710843373493972</v>
       </c>
       <c r="AD77">
-        <f>V77-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>71</v>
       </c>
@@ -8570,7 +8580,7 @@
         <v>181</v>
       </c>
       <c r="K78" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L78" t="s">
@@ -8613,27 +8623,27 @@
         <v>34</v>
       </c>
       <c r="Z78">
-        <f>T78/W78</f>
+        <f t="shared" si="11"/>
         <v>10.266666666666667</v>
       </c>
       <c r="AA78">
-        <f>Z78-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>2.8275460379865729</v>
       </c>
       <c r="AB78">
-        <f>R78-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>0.97468354430379733</v>
       </c>
       <c r="AC78">
-        <f>S78/(-110+17.25*Q78)*100-100</f>
+        <f t="shared" si="14"/>
         <v>-27.710843373493972</v>
       </c>
       <c r="AD78">
-        <f>V78-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>74</v>
       </c>
@@ -8656,7 +8666,7 @@
         <v>110</v>
       </c>
       <c r="K79" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L79" t="s">
@@ -8699,27 +8709,27 @@
         <v>34</v>
       </c>
       <c r="Z79">
-        <f>T79/W79</f>
+        <f t="shared" si="11"/>
         <v>8.7272727272727266</v>
       </c>
       <c r="AA79">
-        <f>Z79-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>1.288152098592632</v>
       </c>
       <c r="AB79">
-        <f>R79-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>-0.52531645569620267</v>
       </c>
       <c r="AC79">
-        <f>S79/(-110+17.25*Q79)*100-100</f>
+        <f t="shared" si="14"/>
         <v>8.533916849015327</v>
       </c>
       <c r="AD79">
-        <f>V79-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>75</v>
       </c>
@@ -8742,7 +8752,7 @@
         <v>150</v>
       </c>
       <c r="K80" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L80" t="s">
@@ -8785,23 +8795,23 @@
         <v>34</v>
       </c>
       <c r="Z80">
-        <f>T80/W80</f>
+        <f t="shared" si="11"/>
         <v>9.8181818181818183</v>
       </c>
       <c r="AA80">
-        <f>Z80-(AVERAGE(Z:Z))</f>
+        <f t="shared" si="12"/>
         <v>2.3790611895017237</v>
       </c>
       <c r="AB80">
-        <f>R80-AVERAGE(R:R)</f>
+        <f t="shared" si="13"/>
         <v>0.47468354430379733</v>
       </c>
       <c r="AC80">
-        <f>S80/(-110+17.25*Q80)*100-100</f>
+        <f t="shared" si="14"/>
         <v>4.6466224131198572</v>
       </c>
       <c r="AD80">
-        <f>V80-AVERAGE(V:V)</f>
+        <f t="shared" si="15"/>
         <v>-2.924050632911392</v>
       </c>
     </row>
@@ -8818,5 +8828,6 @@
     <hyperlink ref="B8" r:id="rId5" xr:uid="{637EE4E2-122C-4B62-A3AA-BF8885E38863}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/data/manualdata/_manualdata_master.xlsx
+++ b/data/manualdata/_manualdata_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\notebookpick\data\manualdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED65DED-2281-4195-BBE6-362A6B647278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0171FC-DCAC-4713-A939-76C918CB766F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{52B35C0C-4AC1-4CD7-A119-F59BBD510595}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{52B35C0C-4AC1-4CD7-A119-F59BBD510595}"/>
   </bookViews>
   <sheets>
     <sheet name="전체" sheetId="5" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="245">
   <si>
     <t>id</t>
   </si>
@@ -44,9 +44,6 @@
     <t>brand</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>variant</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
     <t>market</t>
   </si>
   <si>
-    <t>lasust_update</t>
-  </si>
-  <si>
     <t>battery_time</t>
   </si>
   <si>
@@ -125,9 +119,6 @@
     <t>acer</t>
   </si>
   <si>
-    <t>스위프트 14, u7 258v</t>
-  </si>
-  <si>
     <t>u7 258v</t>
   </si>
   <si>
@@ -143,18 +134,12 @@
     <t>https://www.coupang.com/vp/products/8906849724</t>
   </si>
   <si>
-    <t>스위프트 고 14, u5 225h</t>
-  </si>
-  <si>
     <t>u5 225h</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/9047218674?itemId=26552559197&amp;vendorItemId=93526407709</t>
   </si>
   <si>
-    <t>스위프트 라이트 16, u5 115u</t>
-  </si>
-  <si>
     <t>u5 115u</t>
   </si>
   <si>
@@ -164,9 +149,6 @@
     <t>https://www.coupang.com/vp/products/8773621852?itemId=25522224881&amp;vendorItemId=92514067366</t>
   </si>
   <si>
-    <t>아스파이어 라이트 16, i3 1305u</t>
-  </si>
-  <si>
     <t>램 장착 권장</t>
   </si>
   <si>
@@ -179,18 +161,12 @@
     <t>https://www.coupang.com/vp/products/8708067859?itemId=25326317735&amp;vendorItemId=92321198996</t>
   </si>
   <si>
-    <t>아스파이어 라이트 16, i5 1335u</t>
-  </si>
-  <si>
     <t>i5 1335u</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8579806173?itemId=24867355094&amp;vendorItemId=91874318252</t>
   </si>
   <si>
-    <t>asus</t>
-  </si>
-  <si>
     <t>[ARM] 젠북 A14, X1-26</t>
   </si>
   <si>
@@ -200,57 +176,36 @@
     <t>https://www.coupang.com/vp/products/8982838372?itemId=26302272690&amp;vendorItemId=93279989300</t>
   </si>
   <si>
-    <t>비보북 16, i5 120u</t>
-  </si>
-  <si>
     <t>i5 120u</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8593723288?itemId=24917488765&amp;vendorItemId=91923824133</t>
   </si>
   <si>
-    <t>비보북 16, u5 225h</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8620714025</t>
   </si>
   <si>
-    <t>비보북 18, r7 260</t>
-  </si>
-  <si>
     <t>r7 260</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8814642136?itemId=25682243168&amp;vendorItemId=92671562598</t>
   </si>
   <si>
-    <t>비보북 s16, i5 13420h</t>
-  </si>
-  <si>
     <t>i5 13420h</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8941702848?itemId=26149371639&amp;vendorItemId=93129360141</t>
   </si>
   <si>
-    <t>비보북 s16, r7 350</t>
-  </si>
-  <si>
     <t>r7 350</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8952483892?itemId=26187891331&amp;vendorItemId=93167335508</t>
   </si>
   <si>
-    <t>비보북 s16, u5 225h</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8539448432?itemId=24722655866&amp;vendorItemId=91731863931</t>
   </si>
   <si>
-    <t>젠북 14, u7 255h</t>
-  </si>
-  <si>
     <t>u7 255h</t>
   </si>
   <si>
@@ -263,9 +218,6 @@
     <t>https://www.coupang.com/vp/products/8410862361?itemId=24318990059&amp;vendorItemId=91334761271</t>
   </si>
   <si>
-    <t>젠북 s14, u5 226v</t>
-  </si>
-  <si>
     <t>그레이</t>
   </si>
   <si>
@@ -281,54 +233,33 @@
     <t>https://www.coupang.com/vp/products/8544270516?itemId=24738885102&amp;vendorItemId=91747617943</t>
   </si>
   <si>
-    <t>젠북 s16, u7 258v</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8620630703?itemId=25010066108&amp;vendorItemId=92015050332</t>
   </si>
   <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>노트북 14, i5 1334u</t>
-  </si>
-  <si>
     <t>i5 1334u</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8099175514?itemId=22901913166&amp;vendorItemId=89936416843</t>
   </si>
   <si>
-    <t>노트북 15, r5 7430u</t>
-  </si>
-  <si>
     <t>r5 7430u</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8703035211?itemId=25273784880&amp;vendorItemId=92269450641</t>
   </si>
   <si>
-    <t>노트북 255 G10, r5 7530u</t>
-  </si>
-  <si>
     <t>r5 7530u</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8849752787?itemId=25016750920&amp;vendorItemId=92021599232</t>
   </si>
   <si>
-    <t>엘리트북 울트라 g1i 14, u5 228v</t>
-  </si>
-  <si>
     <t>u5 228v</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8648574647?itemId=25102068021&amp;vendorItemId=92104783093</t>
   </si>
   <si>
-    <t>옴니북 3 14, i3 1315u</t>
-  </si>
-  <si>
     <t>i3 1315u</t>
   </si>
   <si>
@@ -338,69 +269,36 @@
     <t>https://www.coupang.com/vp/products/8785877887?itemId=25566791886&amp;vendorItemId=92557979714</t>
   </si>
   <si>
-    <t>옴니북 3 15.6, r7 340</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8740557641?itemId=25402248933&amp;vendorItemId=92395806929</t>
   </si>
   <si>
-    <t>옴니북 5 nagi 16, r5 340</t>
-  </si>
-  <si>
     <t>r5 340</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8743114968?itemId=25409271495&amp;vendorItemId=92402704438</t>
   </si>
   <si>
-    <t>옴니북 7 에어로 13, r7 350</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8688208941?itemId=25224312267&amp;vendorItemId=92220619670</t>
   </si>
   <si>
-    <t>옴니북 x 플립 14, r7 340 oled</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8847574516?itemId=25515379290&amp;vendorItemId=92507314479</t>
   </si>
   <si>
-    <t>옴니북 x 플립 14, u5 226v ips</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8734831107?itemId=25383774207&amp;vendorItemId=92377682363</t>
   </si>
   <si>
-    <t>옴니북 x 플립 14, u5 226v oled</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8829827803?itemId=25383774406&amp;vendorItemId=92377682706</t>
   </si>
   <si>
-    <t>옴니북 x 플립 14, u7 258v oled</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8565613980?itemId=24810120311&amp;vendorItemId=92229848441</t>
   </si>
   <si>
-    <t>옴니북 울트라 플립 14, u5 226v</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8398992443?itemId=24277916398&amp;vendorItemId=91294313138</t>
   </si>
   <si>
-    <t>옴니북 울트라 플립 14, u7 258v</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/9088545835?itemId=26706196132&amp;vendorItemId=93677980039</t>
   </si>
   <si>
-    <t>lenovo</t>
-  </si>
-  <si>
-    <t>V15 G4 AMN, r3 7320u</t>
-  </si>
-  <si>
     <t>r3 7320u</t>
   </si>
   <si>
@@ -413,123 +311,72 @@
     <t>https://www.coupang.com/vp/products/8680039848?itemId=25197742104&amp;vendorItemId=92194389018</t>
   </si>
   <si>
-    <t>씽크북 14arp G7 R5, r5 7535hs</t>
-  </si>
-  <si>
     <t>r5 7535hs</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8146665286?itemId=23167065497&amp;vendorItemId=90199849499</t>
   </si>
   <si>
-    <t>씽크북 14arp G7 R7, r7 7735hs</t>
-  </si>
-  <si>
     <t>r7 7735hs</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8201783041?itemId=23513749012&amp;vendorItemId=90540144557</t>
   </si>
   <si>
-    <t>씽크북 16arp G7 R5, r5 7535hs</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8201783041?itemId=24949700717&amp;vendorItemId=91955595467</t>
   </si>
   <si>
-    <t>씽크북 16arp G7 R7, r7 7735hs</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8760943054?itemId=25474839711&amp;vendorItemId=92467262961</t>
   </si>
   <si>
-    <t>씽크북 16ial g8 u5 3K, u5 225h</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8730924757?itemId=25369154828&amp;vendorItemId=92363325594</t>
   </si>
   <si>
-    <t>아이디어패드 슬림3 14ahp10 oled, r5 8640hs</t>
-  </si>
-  <si>
     <t>r5 8640hs</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8743086948?itemId=25409162113&amp;vendorItemId=92402597630</t>
   </si>
   <si>
-    <t>아이디어패드 슬림3 15ahp10 oled, r5 8640hs</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/9251257445?itemId=27363809908&amp;vendorItemId=94329842260</t>
   </si>
   <si>
-    <t>아이디어패드 슬림3 15ahp10, r5 8640hs</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8789578488?itemId=25368988626&amp;vendorItemId=92363162957</t>
   </si>
   <si>
-    <t>아이디어패드 슬림3 15arp10 oled, r5 7533hs</t>
-  </si>
-  <si>
     <t>r5 7533hs</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8956936394?itemId=26207071340&amp;vendorItemId=93186207320</t>
   </si>
   <si>
-    <t>아이디어패드 슬림3 15iru8, i3 1315u</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8849748058</t>
   </si>
   <si>
-    <t>아이디어패드 슬림5 14akp10, r5 340</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8660625625</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8898341424</t>
   </si>
   <si>
-    <t>아이디어패드 슬림5 14iah10, u5 225h</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8898526670?itemId=26840804658&amp;vendorItemId=93810725946</t>
   </si>
   <si>
-    <t>아이디어패드 슬림5 16akp10, r5 340</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8670201542</t>
   </si>
   <si>
-    <t>아이디어패드 슬림5 16akp10, r7 350</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8883152949</t>
   </si>
   <si>
-    <t>아이디어패드 슬림5 16iah10, u5 225h</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8883267474</t>
   </si>
   <si>
-    <t>아이디어패드 슬림5 16iah10, u7 255h</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8847714479?itemId=25737737037&amp;vendorItemId=92733954991</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8673080963?itemId=25177237369&amp;vendorItemId=92174218910</t>
   </si>
   <si>
-    <t>요가 7 2in1 14ill10, u5 228v</t>
-  </si>
-  <si>
     <t>그레이, 512GB</t>
   </si>
   <si>
@@ -554,51 +401,27 @@
     <t>https://www.coupang.com/vp/products/8670590507?itemId=25169885850&amp;vendorItemId=92167265171</t>
   </si>
   <si>
-    <t>요가 슬림7 14ill10, u5 228v</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8670590493?itemId=25169885815&amp;vendorItemId=92167265169</t>
   </si>
   <si>
-    <t>요가 슬림7 14ill10, u7 258v</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8408971036?itemId=24311993053&amp;vendorItemId=91327841194</t>
   </si>
   <si>
-    <t>요가 슬림7 15ill9, u7 258v</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/7955896989?itemId=21980916755&amp;vendorItemId=89028561695</t>
   </si>
   <si>
-    <t>요가북  9i 13imu9, u7 155u</t>
-  </si>
-  <si>
     <t>u7 155u</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8518435229?itemId=24662380297&amp;vendorItemId=91672792964</t>
   </si>
   <si>
-    <t>lg</t>
-  </si>
-  <si>
-    <t>그램 14, u5 225h</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8518435238?itemId=24662380338&amp;vendorItemId=91672792997</t>
   </si>
   <si>
-    <t>그램프로 16, u5 225h</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/9254540118?itemId=27375892893&amp;vendorItemId=94341788006</t>
   </si>
   <si>
-    <t>그램프로 16, u5 226v</t>
-  </si>
-  <si>
     <t>프리도스</t>
   </si>
   <si>
@@ -611,31 +434,19 @@
     <t>https://www.coupang.com/vp/products/8518435232?itemId=24662380325&amp;vendorItemId=91672792975</t>
   </si>
   <si>
-    <t>그램프로 17, u5 225h</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8518435234?itemId=24662380327&amp;vendorItemId=91672792982</t>
   </si>
   <si>
-    <t>그램프로 360 16, u5 225h</t>
-  </si>
-  <si>
     <t>https://www.coupang.com/vp/products/8826291800?itemId=25753343478&amp;vendorItemId=92741604174</t>
   </si>
   <si>
     <t>microsoft</t>
   </si>
   <si>
-    <t>[ARM] 서피스 랩탑 13, x1p-46</t>
-  </si>
-  <si>
     <t>x1p-46</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8665657438?itemId=23498375950&amp;vendorItemId=90524823846</t>
-  </si>
-  <si>
-    <t>[ARM] 서피스 랩탑 13.8, x1p-64</t>
   </si>
   <si>
     <t>x1p-64</t>
@@ -645,13 +456,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpadx9/thinkpad-x9-aura-edition-15-inch-intel/21q6cto1wwkr3</t>
-  </si>
-  <si>
-    <t>lenovo</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>u5 228v</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -668,9 +472,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpade/thinkpad-e14-gen-7-14-inch-intel-laptop/21u2cto1wwkr2</t>
-  </si>
-  <si>
     <t>ips</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -679,20 +480,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpade/lenovo-thinkpad-e16-gen-3-16-inch-intel/22aycto1wwkr1</t>
-  </si>
-  <si>
-    <t>씽크패드 x13, u5 225H</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>u5 225H</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpadx/thinkpad-x13-gen-6-13-inch-intel/21rkcto1wwkr3</t>
-  </si>
-  <si>
     <t>https://item.gmarket.co.kr/Item?goodscode=4623684498</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -709,22 +500,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>씽크패드 X9-15 gen1, u5 228v</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>씽크패드 e14 gen7, u5 228v</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>씽크패드 e16 gen3, u5 226v</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>프레스티지 16, U7 155H</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>후면포트</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -737,18 +512,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>비보북 S16, r7 350</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>r7 350</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>window</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://item.gmarket.co.kr/Item?goodscode=4572335752</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -765,64 +532,271 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>samsung</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>갤럭시북 4, i3 1315u</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/samsung_mall/products/11256046363</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>갤럭시북 5프로 NT940XHA-K51A, u5 226v</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>네이버</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>갤럭시북 5프로 NT960XHZ-A51A, u5 226v</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>asus</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://item.gmarket.co.kr/Item?goodscode=4563773737</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>i3 1315u</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>r5 340</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>아이디어패드 슬림5 14akp10, r7 350</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이디어패드 슬림5 2in1 16akp10, r7 350</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>u7 258v</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>요가 7 2in1 14ill10, u7 258v</t>
+    <t>name</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>비보북 S16, R7 350</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림3 15ARP10 OLED, R5 7533HS</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림5 16IAH10, U5 225H</t>
+  </si>
+  <si>
+    <t>프레스티지 16, U7 155H</t>
+  </si>
+  <si>
+    <t>갤럭시북 5프로 NT960XHZ-A51A, U5 226V</t>
+  </si>
+  <si>
+    <t>갤럭시북 5프로 NT940XHA-K51A, U5 226V</t>
+  </si>
+  <si>
+    <t>씽크패드 X13, U5 225H</t>
+  </si>
+  <si>
+    <t>스위프트 라이트 16, U5 115U</t>
+  </si>
+  <si>
+    <t>스위프트 고 14, U5 225H</t>
+  </si>
+  <si>
+    <t>스위프트 14, U7 258V</t>
+  </si>
+  <si>
+    <t>비보북 18, R7 260</t>
+  </si>
+  <si>
+    <t>비보북 16, U5 225H</t>
+  </si>
+  <si>
+    <t>비보북 S16, U5 225H</t>
+  </si>
+  <si>
+    <t>젠북 S14, U5 226V</t>
+  </si>
+  <si>
+    <t>젠북 14, U7 255H</t>
+  </si>
+  <si>
+    <t>젠북 S16, U7 258V</t>
+  </si>
+  <si>
+    <t>옴니북 5 NAGI 16, R5 340</t>
+  </si>
+  <si>
+    <t>옴니북 X 플립 14, R7 340 OLED</t>
+  </si>
+  <si>
+    <t>노트북 15, R5 7430U</t>
+  </si>
+  <si>
+    <t>노트북 255 G10, R5 7530U</t>
+  </si>
+  <si>
+    <t>옴니북 3 15.6, R7 340</t>
+  </si>
+  <si>
+    <t>옴니북 7 에어로 13, R7 350</t>
+  </si>
+  <si>
+    <t>옴니북 X 플립 14, U5 226V IPS</t>
+  </si>
+  <si>
+    <t>옴니북 X 플립 14, U5 226V OLED</t>
+  </si>
+  <si>
+    <t>옴니북 울트라 플립 14, U5 226V</t>
+  </si>
+  <si>
+    <t>엘리트북 울트라 G1I 14, U5 228V</t>
+  </si>
+  <si>
+    <t>옴니북 X 플립 14, U7 258V OLED</t>
+  </si>
+  <si>
+    <t>옴니북 울트라 플립 14, U7 258V</t>
+  </si>
+  <si>
+    <t>V15 G4 AMN, R3 7320U</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림5 14AKP10, R5 340</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림5 16AKP10, R5 340</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림5 14AKP10, R7 350</t>
+  </si>
+  <si>
+    <t>씽크북 14ARP G7 R5, R5 7535HS</t>
+  </si>
+  <si>
+    <t>씽크북 16ARP G7 R5, R5 7535HS</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림3 14AHP10 OLED, R5 8640HS</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림3 15AHP10 OLED, R5 8640HS</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림3 15AHP10, R5 8640HS</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림5 16AKP10, R7 350</t>
+  </si>
+  <si>
+    <t>씽크북 16IAL G8 U5 3K, U5 225H</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림5 14IAH10, U5 225H</t>
+  </si>
+  <si>
+    <t>요가 슬림7 14ILL10, U5 228V</t>
+  </si>
+  <si>
+    <t>요가북  9I 13IMU9, U7 155U</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림5 16IAH10, U7 255H</t>
+  </si>
+  <si>
+    <t>요가 슬림7 14ILL10, U7 258V</t>
+  </si>
+  <si>
+    <t>요가 슬림7 15ILL9, U7 258V</t>
+  </si>
+  <si>
+    <t>그램 14, U5 225H</t>
+  </si>
+  <si>
+    <t>그램프로 16, U5 225H</t>
+  </si>
+  <si>
+    <t>그램프로 17, U5 225H</t>
+  </si>
+  <si>
+    <t>그램프로 360 16, U5 225H</t>
+  </si>
+  <si>
+    <t>그램프로 16, U5 226V</t>
+  </si>
+  <si>
+    <t>[ARM] 서피스 랩탑 13, X1P-46</t>
+  </si>
+  <si>
+    <t>[ARM] 서피스 랩탑 13.8, X1P-64</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아스파이어 라이트 16, i5 1335U</t>
+  </si>
+  <si>
+    <t>비보북 16, i5 120U</t>
+  </si>
+  <si>
+    <t>비보북 S16, i5 13420H</t>
+  </si>
+  <si>
+    <t>노트북 14, i5 1334U</t>
+  </si>
+  <si>
+    <t>갤럭시북 4, i3 1315U</t>
+  </si>
+  <si>
+    <t>아스파이어 라이트 16, i3 1305U</t>
+  </si>
+  <si>
+    <t>옴니북 3 14, i3 1315U</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림3 15IRU8, i3 1315U</t>
+  </si>
+  <si>
+    <t>요가 7 2in1 14ILL10, U5 228V</t>
+  </si>
+  <si>
+    <t>씽크패드 E16 gen3, U5 226V</t>
+  </si>
+  <si>
+    <t>씽크패드 X9-15 gen1, U5 228V</t>
+  </si>
+  <si>
+    <t>씽크패드 E14 gen7, U5 228V</t>
+  </si>
+  <si>
+    <t>씽크북 14ARP G7, R7 7735HS</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>씽크북 16ARP G7, R7 7735HS</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>not_selling</t>
+  </si>
+  <si>
+    <t>window</t>
+  </si>
+  <si>
+    <t>아이디어패드 슬림5 2in1 16AKP10, R7 350</t>
+  </si>
+  <si>
+    <t>요가 7 2in1 14ILL10, U7 258V</t>
+  </si>
+  <si>
+    <t>Lenovo</t>
+  </si>
+  <si>
+    <t>www.Lenovo.com/kr/ko/p/laptops/thinkpad/thinkpadx/thinkpad-x13-gen-6-13-inch-intel/21rkcto1wwkr3</t>
+  </si>
+  <si>
+    <t>www.Lenovo.com/kr/ko/p/laptops/thinkpad/thinkpade/Lenovo-thinkpad-e16-gen-3-16-inch-intel/22aycto1wwkr1</t>
+  </si>
+  <si>
+    <t>www.Lenovo.com/kr/ko/p/laptops/thinkpad/thinkpadx9/thinkpad-x9-aura-edition-15-inch-intel/21q6cto1wwkr3</t>
+  </si>
+  <si>
+    <t>www.Lenovo.com/kr/ko/p/laptops/thinkpad/thinkpade/thinkpad-e14-gen-7-14-inch-intel-laptop/21u2cto1wwkr2</t>
+  </si>
+  <si>
+    <t>ASUS</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>LG</t>
+  </si>
+  <si>
+    <t>last_update</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SAMSUNG</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/SAMSUNG_mall/products/11256046363</t>
   </si>
 </sst>
 </file>
@@ -1814,14 +1788,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50411788-00EA-46D9-AD03-A2E5A7239D60}">
   <dimension ref="A1:AD80"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1832,105 +1807,105 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>20</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>140</v>
@@ -1943,13 +1918,13 @@
         <v>-7.1428571428571423</v>
       </c>
       <c r="L2" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="M2">
         <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="O2">
         <v>512</v>
@@ -1970,7 +1945,7 @@
         <v>75</v>
       </c>
       <c r="U2" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="V2">
         <v>7</v>
@@ -1979,7 +1954,7 @@
         <v>9.5</v>
       </c>
       <c r="X2" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="Z2">
         <f t="shared" ref="Z2:Z33" si="0">T2/W2</f>
@@ -2002,27 +1977,27 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>72</v>
@@ -2031,17 +2006,17 @@
         <v>64</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K66" si="5">IF(X3&lt;&gt;"쿠팡", ((J3-I3)/I3)*100, "")</f>
+        <f>IF(X3&lt;&gt;"쿠팡", ((J3-I3)/I3)*100, "")</f>
         <v>-11.111111111111111</v>
       </c>
       <c r="L3" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="M3">
         <v>8</v>
       </c>
       <c r="N3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O3">
         <v>256</v>
@@ -2062,7 +2037,7 @@
         <v>60</v>
       </c>
       <c r="U3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V3">
         <v>5</v>
@@ -2071,7 +2046,7 @@
         <v>11</v>
       </c>
       <c r="X3" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="Z3">
         <f t="shared" si="0"/>
@@ -2094,24 +2069,24 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>125</v>
@@ -2120,17 +2095,17 @@
         <v>118</v>
       </c>
       <c r="K4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K3:K66" si="5">IF(X4&lt;&gt;"쿠팡", ((J4-I4)/I4)*100, "")</f>
         <v>-5.6000000000000005</v>
       </c>
       <c r="L4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M4">
         <v>32</v>
       </c>
       <c r="N4" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O4">
         <v>512</v>
@@ -2151,7 +2126,7 @@
         <v>60</v>
       </c>
       <c r="U4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -2160,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="X4" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
@@ -2183,27 +2158,27 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>224</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>232</v>
+        <v>157</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>160</v>
@@ -2212,17 +2187,17 @@
         <v>143</v>
       </c>
       <c r="K5">
-        <f t="shared" si="5"/>
+        <f>IF(X5&lt;&gt;"쿠팡", ((J5-I5)/I5)*100, "")</f>
         <v>-10.625</v>
       </c>
       <c r="L5" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M5">
         <v>32</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O5">
         <v>512</v>
@@ -2243,7 +2218,7 @@
         <v>70</v>
       </c>
       <c r="U5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -2252,7 +2227,7 @@
         <v>7.25</v>
       </c>
       <c r="X5" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
@@ -2275,27 +2250,27 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>224</v>
+        <v>151</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>130</v>
@@ -2308,13 +2283,13 @@
         <v>-7.6923076923076925</v>
       </c>
       <c r="L6" t="s">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="M6">
         <v>16</v>
       </c>
       <c r="N6" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="O6">
         <v>512</v>
@@ -2335,7 +2310,7 @@
         <v>100</v>
       </c>
       <c r="U6" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -2344,7 +2319,7 @@
         <v>10.25</v>
       </c>
       <c r="X6" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="Z6">
         <f t="shared" si="0"/>
@@ -2367,24 +2342,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>77</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>70</v>
@@ -2393,17 +2368,17 @@
         <v>76</v>
       </c>
       <c r="K7">
-        <f t="shared" si="5"/>
+        <f>IF(X7&lt;&gt;"쿠팡", ((J7-I7)/I7)*100, "")</f>
         <v>8.5714285714285712</v>
       </c>
       <c r="L7" t="s">
-        <v>242</v>
+        <v>75</v>
       </c>
       <c r="M7">
         <v>16</v>
       </c>
       <c r="N7" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="O7">
         <v>256</v>
@@ -2424,7 +2399,7 @@
         <v>54</v>
       </c>
       <c r="U7" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="V7">
         <v>3</v>
@@ -2433,7 +2408,7 @@
         <v>10.25</v>
       </c>
       <c r="X7" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
@@ -2456,24 +2431,24 @@
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>79</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D8" t="s">
-        <v>239</v>
+        <v>168</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>175</v>
@@ -2486,13 +2461,13 @@
         <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="O8">
         <v>256</v>
@@ -2513,7 +2488,7 @@
         <v>76</v>
       </c>
       <c r="U8" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -2522,7 +2497,7 @@
         <v>7.5</v>
       </c>
       <c r="X8" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="Z8">
         <f t="shared" si="0"/>
@@ -2545,18 +2520,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>78</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D9" t="s">
-        <v>237</v>
+        <v>169</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -2575,13 +2550,13 @@
         <v>9.0909090909090917</v>
       </c>
       <c r="L9" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="M9">
         <v>16</v>
       </c>
       <c r="N9" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="O9">
         <v>256</v>
@@ -2602,7 +2577,7 @@
         <v>63</v>
       </c>
       <c r="U9" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -2611,7 +2586,7 @@
         <v>6.75</v>
       </c>
       <c r="X9" t="s">
-        <v>238</v>
+        <v>159</v>
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
@@ -2634,24 +2609,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C10" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D10" t="s">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>202</v>
+        <v>139</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2667,13 +2642,13 @@
         <v>6.25</v>
       </c>
       <c r="L10" t="s">
-        <v>214</v>
+        <v>146</v>
       </c>
       <c r="M10">
         <v>32</v>
       </c>
       <c r="N10" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="O10">
         <v>256</v>
@@ -2694,7 +2669,7 @@
         <v>55</v>
       </c>
       <c r="U10" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -2703,7 +2678,7 @@
         <v>6</v>
       </c>
       <c r="X10" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="Z10">
         <f t="shared" si="0"/>
@@ -2726,24 +2701,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="C11" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D11" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>202</v>
+        <v>139</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2759,13 +2734,13 @@
         <v>-6.4</v>
       </c>
       <c r="L11" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="M11">
         <v>16</v>
       </c>
       <c r="N11" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="O11">
         <v>256</v>
@@ -2786,7 +2761,7 @@
         <v>64</v>
       </c>
       <c r="U11" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -2795,7 +2770,7 @@
         <v>7.5</v>
       </c>
       <c r="X11" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="Z11">
         <f t="shared" si="0"/>
@@ -2818,24 +2793,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="C12" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D12" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>202</v>
+        <v>139</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2851,13 +2826,13 @@
         <v>-5.1282051282051277</v>
       </c>
       <c r="L12" t="s">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="M12">
         <v>32</v>
       </c>
       <c r="N12" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="O12">
         <v>512</v>
@@ -2878,7 +2853,7 @@
         <v>80</v>
       </c>
       <c r="U12" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -2887,7 +2862,7 @@
         <v>7.5</v>
       </c>
       <c r="X12" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="Z12">
         <f t="shared" si="0"/>
@@ -2910,24 +2885,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="C13" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D13" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>202</v>
+        <v>139</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2943,13 +2918,13 @@
         <v>-1.4814814814814816</v>
       </c>
       <c r="L13" t="s">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="M13">
         <v>32</v>
       </c>
       <c r="N13" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="O13">
         <v>512</v>
@@ -2970,7 +2945,7 @@
         <v>64</v>
       </c>
       <c r="U13" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -2979,7 +2954,7 @@
         <v>6.75</v>
       </c>
       <c r="X13" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="Z13">
         <f t="shared" si="0"/>
@@ -3002,24 +2977,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>221</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -3032,13 +3007,13 @@
         <v/>
       </c>
       <c r="L14" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O14">
         <v>512</v>
@@ -3059,7 +3034,7 @@
         <v>58</v>
       </c>
       <c r="U14" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V14">
         <v>2</v>
@@ -3068,7 +3043,7 @@
         <v>10.25</v>
       </c>
       <c r="X14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z14">
         <f t="shared" si="0"/>
@@ -3091,24 +3066,24 @@
         <v>-3.924050632911392</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>216</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -3121,13 +3096,13 @@
         <v/>
       </c>
       <c r="L15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M15">
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O15">
         <v>512</v>
@@ -3148,7 +3123,7 @@
         <v>58</v>
       </c>
       <c r="U15" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V15">
         <v>3</v>
@@ -3157,7 +3132,7 @@
         <v>10.25</v>
       </c>
       <c r="X15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z15">
         <f t="shared" si="0"/>
@@ -3180,18 +3155,18 @@
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>171</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -3207,13 +3182,13 @@
         <v/>
       </c>
       <c r="L16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M16">
         <v>16</v>
       </c>
       <c r="N16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O16">
         <v>512</v>
@@ -3234,7 +3209,7 @@
         <v>58</v>
       </c>
       <c r="U16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -3243,7 +3218,7 @@
         <v>9</v>
       </c>
       <c r="X16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z16">
         <f t="shared" si="0"/>
@@ -3266,18 +3241,18 @@
         <v>-1.924050632911392</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>172</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -3293,13 +3268,13 @@
         <v/>
       </c>
       <c r="L17" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M17">
         <v>16</v>
       </c>
       <c r="N17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O17">
         <v>512</v>
@@ -3320,7 +3295,7 @@
         <v>63</v>
       </c>
       <c r="U17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -3329,7 +3304,7 @@
         <v>9.25</v>
       </c>
       <c r="X17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z17">
         <f t="shared" si="0"/>
@@ -3352,18 +3327,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>173</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -3379,13 +3354,13 @@
         <v/>
       </c>
       <c r="L18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M18">
         <v>32</v>
       </c>
       <c r="N18" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O18">
         <v>512</v>
@@ -3406,7 +3381,7 @@
         <v>65</v>
       </c>
       <c r="U18" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -3415,7 +3390,7 @@
         <v>7.25</v>
       </c>
       <c r="X18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z18">
         <f t="shared" si="0"/>
@@ -3438,24 +3413,24 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>217</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -3468,13 +3443,13 @@
         <v/>
       </c>
       <c r="L19" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M19">
         <v>8</v>
       </c>
       <c r="N19" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O19">
         <v>512</v>
@@ -3495,7 +3470,7 @@
         <v>42</v>
       </c>
       <c r="U19" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V19">
         <v>3</v>
@@ -3504,7 +3479,7 @@
         <v>10.25</v>
       </c>
       <c r="X19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z19">
         <f t="shared" si="0"/>
@@ -3527,18 +3502,18 @@
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>218</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -3554,13 +3529,13 @@
         <v/>
       </c>
       <c r="L20" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="M20">
         <v>16</v>
       </c>
       <c r="N20" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O20">
         <v>512</v>
@@ -3581,7 +3556,7 @@
         <v>70</v>
       </c>
       <c r="U20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V20">
         <v>2</v>
@@ -3590,7 +3565,7 @@
         <v>11.75</v>
       </c>
       <c r="X20" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z20">
         <f t="shared" si="0"/>
@@ -3613,18 +3588,18 @@
         <v>-3.924050632911392</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -3640,13 +3615,13 @@
         <v/>
       </c>
       <c r="L21" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M21">
         <v>16</v>
       </c>
       <c r="N21" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O21">
         <v>512</v>
@@ -3667,7 +3642,7 @@
         <v>70</v>
       </c>
       <c r="U21" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -3676,7 +3651,7 @@
         <v>9.5</v>
       </c>
       <c r="X21" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z21">
         <f t="shared" si="0"/>
@@ -3699,18 +3674,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>164</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -3726,13 +3701,13 @@
         <v/>
       </c>
       <c r="L22" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M22">
         <v>16</v>
       </c>
       <c r="N22" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O22">
         <v>512</v>
@@ -3753,7 +3728,7 @@
         <v>70</v>
       </c>
       <c r="U22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -3762,7 +3737,7 @@
         <v>9.25</v>
       </c>
       <c r="X22" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z22">
         <f t="shared" si="0"/>
@@ -3785,18 +3760,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -3812,13 +3787,13 @@
         <v/>
       </c>
       <c r="L23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M23">
         <v>16</v>
       </c>
       <c r="N23" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O23">
         <v>512</v>
@@ -3839,7 +3814,7 @@
         <v>42</v>
       </c>
       <c r="U23" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -3848,7 +3823,7 @@
         <v>8.75</v>
       </c>
       <c r="X23" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z23">
         <f t="shared" si="0"/>
@@ -3871,18 +3846,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>176</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -3898,13 +3873,13 @@
         <v/>
       </c>
       <c r="L24" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M24">
         <v>16</v>
       </c>
       <c r="N24" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O24">
         <v>512</v>
@@ -3925,7 +3900,7 @@
         <v>70</v>
       </c>
       <c r="U24" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -3934,7 +3909,7 @@
         <v>9.25</v>
       </c>
       <c r="X24" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z24">
         <f t="shared" si="0"/>
@@ -3957,24 +3932,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3987,13 +3962,13 @@
         <v/>
       </c>
       <c r="L25" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M25">
         <v>16</v>
       </c>
       <c r="N25" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="O25">
         <v>512</v>
@@ -4014,7 +3989,7 @@
         <v>72</v>
       </c>
       <c r="U25" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -4023,7 +3998,7 @@
         <v>7.25</v>
       </c>
       <c r="X25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z25">
         <f t="shared" si="0"/>
@@ -4046,24 +4021,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -4076,13 +4051,13 @@
         <v/>
       </c>
       <c r="L26" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M26">
         <v>16</v>
       </c>
       <c r="N26" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="O26">
         <v>512</v>
@@ -4103,7 +4078,7 @@
         <v>72</v>
       </c>
       <c r="U26" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V26">
         <v>7</v>
@@ -4112,7 +4087,7 @@
         <v>7.25</v>
       </c>
       <c r="X26" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z26">
         <f t="shared" si="0"/>
@@ -4135,18 +4110,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -4162,13 +4137,13 @@
         <v/>
       </c>
       <c r="L27" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="M27">
         <v>16</v>
       </c>
       <c r="N27" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="O27">
         <v>512</v>
@@ -4189,7 +4164,7 @@
         <v>75</v>
       </c>
       <c r="U27" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -4198,7 +4173,7 @@
         <v>9.25</v>
       </c>
       <c r="X27" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z27">
         <f t="shared" si="0"/>
@@ -4221,18 +4196,18 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -4248,13 +4223,13 @@
         <v/>
       </c>
       <c r="L28" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="M28">
         <v>32</v>
       </c>
       <c r="N28" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="O28">
         <v>512</v>
@@ -4275,7 +4250,7 @@
         <v>75</v>
       </c>
       <c r="U28" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -4284,7 +4259,7 @@
         <v>9.25</v>
       </c>
       <c r="X28" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z28">
         <f t="shared" si="0"/>
@@ -4307,18 +4282,18 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -4334,13 +4309,13 @@
         <v/>
       </c>
       <c r="L29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M29">
         <v>32</v>
       </c>
       <c r="N29" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="O29">
         <v>1024</v>
@@ -4361,7 +4336,7 @@
         <v>78</v>
       </c>
       <c r="U29" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -4370,7 +4345,7 @@
         <v>8</v>
       </c>
       <c r="X29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z29">
         <f t="shared" si="0"/>
@@ -4393,18 +4368,18 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -4416,17 +4391,17 @@
         <v>110</v>
       </c>
       <c r="K30" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X30&lt;&gt;"쿠팡", ((J30-I30)/I30)*100, "")</f>
         <v/>
       </c>
       <c r="L30" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M30">
         <v>16</v>
       </c>
       <c r="N30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O30">
         <v>512</v>
@@ -4447,7 +4422,7 @@
         <v>48</v>
       </c>
       <c r="U30" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V30">
         <v>3</v>
@@ -4456,7 +4431,7 @@
         <v>5.5</v>
       </c>
       <c r="X30" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z30">
         <f t="shared" si="0"/>
@@ -4479,18 +4454,18 @@
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -4502,17 +4477,17 @@
         <v>45</v>
       </c>
       <c r="K31" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X31&lt;&gt;"쿠팡", ((J31-I31)/I31)*100, "")</f>
         <v/>
       </c>
       <c r="L31" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="M31">
         <v>8</v>
       </c>
       <c r="N31" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O31">
         <v>256</v>
@@ -4533,7 +4508,7 @@
         <v>41</v>
       </c>
       <c r="U31" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V31">
         <v>3</v>
@@ -4542,7 +4517,7 @@
         <v>9.5</v>
       </c>
       <c r="X31" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z31">
         <f t="shared" si="0"/>
@@ -4565,24 +4540,24 @@
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -4591,17 +4566,17 @@
         <v>45</v>
       </c>
       <c r="K32" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X32&lt;&gt;"쿠팡", ((J32-I32)/I32)*100, "")</f>
         <v/>
       </c>
       <c r="L32" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="M32">
         <v>8</v>
       </c>
       <c r="N32" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O32">
         <v>256</v>
@@ -4622,7 +4597,7 @@
         <v>41</v>
       </c>
       <c r="U32" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -4631,7 +4606,7 @@
         <v>9.5</v>
       </c>
       <c r="X32" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z32">
         <f t="shared" si="0"/>
@@ -4654,18 +4629,18 @@
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>180</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -4677,17 +4652,17 @@
         <v>78</v>
       </c>
       <c r="K33" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X33&lt;&gt;"쿠팡", ((J33-I33)/I33)*100, "")</f>
         <v/>
       </c>
       <c r="L33" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="M33">
         <v>16</v>
       </c>
       <c r="N33" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O33">
         <v>512</v>
@@ -4708,7 +4683,7 @@
         <v>43</v>
       </c>
       <c r="U33" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V33">
         <v>5</v>
@@ -4717,7 +4692,7 @@
         <v>8.75</v>
       </c>
       <c r="X33" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z33">
         <f t="shared" si="0"/>
@@ -4740,18 +4715,18 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -4763,17 +4738,17 @@
         <v>126</v>
       </c>
       <c r="K34" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X34&lt;&gt;"쿠팡", ((J34-I34)/I34)*100, "")</f>
         <v/>
       </c>
       <c r="L34" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="M34">
         <v>16</v>
       </c>
       <c r="N34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O34">
         <v>512</v>
@@ -4794,7 +4769,7 @@
         <v>59</v>
       </c>
       <c r="U34" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -4803,7 +4778,7 @@
         <v>9.25</v>
       </c>
       <c r="X34" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z34">
         <f t="shared" ref="Z34:Z65" si="6">T34/W34</f>
@@ -4826,24 +4801,24 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -4852,17 +4827,17 @@
         <v>47</v>
       </c>
       <c r="K35" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X35&lt;&gt;"쿠팡", ((J35-I35)/I35)*100, "")</f>
         <v/>
       </c>
       <c r="L35" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="M35">
         <v>8</v>
       </c>
       <c r="N35" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O35">
         <v>256</v>
@@ -4883,7 +4858,7 @@
         <v>41</v>
       </c>
       <c r="U35" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V35">
         <v>3</v>
@@ -4892,7 +4867,7 @@
         <v>9.75</v>
       </c>
       <c r="X35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z35">
         <f t="shared" si="6"/>
@@ -4915,18 +4890,18 @@
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -4938,17 +4913,17 @@
         <v>50</v>
       </c>
       <c r="K36" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X36&lt;&gt;"쿠팡", ((J36-I36)/I36)*100, "")</f>
         <v/>
       </c>
       <c r="L36" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="M36">
         <v>8</v>
       </c>
       <c r="N36" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O36">
         <v>256</v>
@@ -4969,7 +4944,7 @@
         <v>41</v>
       </c>
       <c r="U36" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V36">
         <v>3</v>
@@ -4978,7 +4953,7 @@
         <v>9</v>
       </c>
       <c r="X36" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z36">
         <f t="shared" si="6"/>
@@ -5001,18 +4976,18 @@
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D37" t="s">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -5024,17 +4999,17 @@
         <v>72</v>
       </c>
       <c r="K37" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X37&lt;&gt;"쿠팡", ((J37-I37)/I37)*100, "")</f>
         <v/>
       </c>
       <c r="L37" t="s">
-        <v>243</v>
+        <v>161</v>
       </c>
       <c r="M37">
         <v>16</v>
       </c>
       <c r="N37" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O37">
         <v>256</v>
@@ -5055,7 +5030,7 @@
         <v>41</v>
       </c>
       <c r="U37" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V37">
         <v>5</v>
@@ -5064,7 +5039,7 @@
         <v>8.75</v>
       </c>
       <c r="X37" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z37">
         <f t="shared" si="6"/>
@@ -5087,18 +5062,18 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -5110,17 +5085,17 @@
         <v>133</v>
       </c>
       <c r="K38" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X38&lt;&gt;"쿠팡", ((J38-I38)/I38)*100, "")</f>
         <v/>
       </c>
       <c r="L38" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M38">
         <v>32</v>
       </c>
       <c r="N38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O38">
         <v>512</v>
@@ -5141,7 +5116,7 @@
         <v>43</v>
       </c>
       <c r="U38" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V38">
         <v>7</v>
@@ -5150,7 +5125,7 @@
         <v>8</v>
       </c>
       <c r="X38" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z38">
         <f t="shared" si="6"/>
@@ -5173,18 +5148,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D39" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5196,17 +5171,17 @@
         <v>107</v>
       </c>
       <c r="K39" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X39&lt;&gt;"쿠팡", ((J39-I39)/I39)*100, "")</f>
         <v/>
       </c>
       <c r="L39" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M39">
         <v>16</v>
       </c>
       <c r="N39" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O39">
         <v>512</v>
@@ -5227,7 +5202,7 @@
         <v>59</v>
       </c>
       <c r="U39" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V39">
         <v>7</v>
@@ -5236,7 +5211,7 @@
         <v>6</v>
       </c>
       <c r="X39" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z39">
         <f t="shared" si="6"/>
@@ -5259,18 +5234,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D40" t="s">
-        <v>112</v>
+        <v>187</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -5286,13 +5261,13 @@
         <v/>
       </c>
       <c r="L40" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M40">
         <v>16</v>
       </c>
       <c r="N40" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O40">
         <v>512</v>
@@ -5313,7 +5288,7 @@
         <v>59</v>
       </c>
       <c r="U40" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -5322,7 +5297,7 @@
         <v>7.25</v>
       </c>
       <c r="X40" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z40">
         <f t="shared" si="6"/>
@@ -5345,18 +5320,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D41" t="s">
-        <v>116</v>
+        <v>188</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -5372,13 +5347,13 @@
         <v/>
       </c>
       <c r="L41" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M41">
         <v>16</v>
       </c>
       <c r="N41" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O41">
         <v>1024</v>
@@ -5399,7 +5374,7 @@
         <v>64</v>
       </c>
       <c r="U41" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V41">
         <v>7</v>
@@ -5408,7 +5383,7 @@
         <v>7.25</v>
       </c>
       <c r="X41" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z41">
         <f t="shared" si="6"/>
@@ -5431,18 +5406,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -5458,13 +5433,13 @@
         <v/>
       </c>
       <c r="L42" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M42">
         <v>32</v>
       </c>
       <c r="N42" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O42">
         <v>512</v>
@@ -5485,7 +5460,7 @@
         <v>64</v>
       </c>
       <c r="U42" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V42">
         <v>7</v>
@@ -5494,7 +5469,7 @@
         <v>6.75</v>
       </c>
       <c r="X42" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z42">
         <f t="shared" si="6"/>
@@ -5517,18 +5492,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D43" t="s">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -5544,13 +5519,13 @@
         <v/>
       </c>
       <c r="L43" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M43">
         <v>32</v>
       </c>
       <c r="N43" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O43">
         <v>512</v>
@@ -5571,7 +5546,7 @@
         <v>59</v>
       </c>
       <c r="U43" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V43">
         <v>8</v>
@@ -5580,7 +5555,7 @@
         <v>7.25</v>
       </c>
       <c r="X43" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z43">
         <f t="shared" si="6"/>
@@ -5603,18 +5578,18 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="D44" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -5630,13 +5605,13 @@
         <v/>
       </c>
       <c r="L44" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <v>32</v>
       </c>
       <c r="N44" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O44">
         <v>1024</v>
@@ -5657,7 +5632,7 @@
         <v>64</v>
       </c>
       <c r="U44" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V44">
         <v>8</v>
@@ -5666,7 +5641,7 @@
         <v>7.25</v>
       </c>
       <c r="X44" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z44">
         <f t="shared" si="6"/>
@@ -5689,18 +5664,18 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D45" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -5716,13 +5691,13 @@
         <v/>
       </c>
       <c r="L45" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="M45">
         <v>8</v>
       </c>
       <c r="N45" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O45">
         <v>512</v>
@@ -5743,7 +5718,7 @@
         <v>45</v>
       </c>
       <c r="U45" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V45">
         <v>3</v>
@@ -5752,7 +5727,7 @@
         <v>10.25</v>
       </c>
       <c r="X45" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z45">
         <f t="shared" si="6"/>
@@ -5775,18 +5750,18 @@
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>34</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D46" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -5802,13 +5777,13 @@
         <v/>
       </c>
       <c r="L46" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="M46">
         <v>16</v>
       </c>
       <c r="N46" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O46">
         <v>256</v>
@@ -5829,7 +5804,7 @@
         <v>47</v>
       </c>
       <c r="U46" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V46">
         <v>2</v>
@@ -5838,7 +5813,7 @@
         <v>10.5</v>
       </c>
       <c r="X46" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z46">
         <f t="shared" si="6"/>
@@ -5861,18 +5836,18 @@
         <v>-3.924050632911392</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D47" t="s">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -5888,13 +5863,13 @@
         <v/>
       </c>
       <c r="L47" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="M47">
         <v>16</v>
       </c>
       <c r="N47" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O47">
         <v>256</v>
@@ -5915,7 +5890,7 @@
         <v>47</v>
       </c>
       <c r="U47" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V47">
         <v>1</v>
@@ -5924,7 +5899,7 @@
         <v>11.25</v>
       </c>
       <c r="X47" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z47">
         <f t="shared" si="6"/>
@@ -5947,18 +5922,18 @@
         <v>-4.924050632911392</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D48" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -5974,13 +5949,13 @@
         <v/>
       </c>
       <c r="L48" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="M48">
         <v>24</v>
       </c>
       <c r="N48" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O48">
         <v>512</v>
@@ -6001,7 +5976,7 @@
         <v>60</v>
       </c>
       <c r="U48" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V48">
         <v>5</v>
@@ -6010,7 +5985,7 @@
         <v>8.5</v>
       </c>
       <c r="X48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z48">
         <f t="shared" si="6"/>
@@ -6033,18 +6008,18 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="C49" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D49" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -6060,13 +6035,13 @@
         <v/>
       </c>
       <c r="L49" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="M49">
         <v>24</v>
       </c>
       <c r="N49" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O49">
         <v>512</v>
@@ -6087,7 +6062,7 @@
         <v>60</v>
       </c>
       <c r="U49" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V49">
         <v>5</v>
@@ -6096,7 +6071,7 @@
         <v>10</v>
       </c>
       <c r="X49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z49">
         <f t="shared" si="6"/>
@@ -6119,18 +6094,18 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D50" t="s">
-        <v>244</v>
+        <v>195</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -6142,17 +6117,17 @@
         <v>126</v>
       </c>
       <c r="K50" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X50&lt;&gt;"쿠팡", ((J50-I50)/I50)*100, "")</f>
         <v/>
       </c>
       <c r="L50" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="M50">
         <v>32</v>
       </c>
       <c r="N50" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O50">
         <v>512</v>
@@ -6173,7 +6148,7 @@
         <v>60</v>
       </c>
       <c r="U50" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V50">
         <v>7</v>
@@ -6182,7 +6157,7 @@
         <v>8.5</v>
       </c>
       <c r="X50" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z50">
         <f t="shared" si="6"/>
@@ -6205,18 +6180,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="C51" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D51" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -6228,17 +6203,17 @@
         <v>133</v>
       </c>
       <c r="K51" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X51&lt;&gt;"쿠팡", ((J51-I51)/I51)*100, "")</f>
         <v/>
       </c>
       <c r="L51" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="M51">
         <v>16</v>
       </c>
       <c r="N51" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O51">
         <v>512</v>
@@ -6259,7 +6234,7 @@
         <v>57</v>
       </c>
       <c r="U51" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V51">
         <v>7</v>
@@ -6268,7 +6243,7 @@
         <v>10</v>
       </c>
       <c r="X51" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z51">
         <f t="shared" si="6"/>
@@ -6291,24 +6266,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -6317,17 +6292,17 @@
         <v>72</v>
       </c>
       <c r="K52" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X52&lt;&gt;"쿠팡", ((J52-I52)/I52)*100, "")</f>
         <v/>
       </c>
       <c r="L52" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="M52">
         <v>8</v>
       </c>
       <c r="N52" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O52">
         <v>256</v>
@@ -6348,7 +6323,7 @@
         <v>60</v>
       </c>
       <c r="U52" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V52">
         <v>5</v>
@@ -6357,7 +6332,7 @@
         <v>11.5</v>
       </c>
       <c r="X52" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z52">
         <f t="shared" si="6"/>
@@ -6380,18 +6355,18 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>35</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C53" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D53" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -6403,17 +6378,17 @@
         <v>64</v>
       </c>
       <c r="K53" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X53&lt;&gt;"쿠팡", ((J53-I53)/I53)*100, "")</f>
         <v/>
       </c>
       <c r="L53" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="M53">
         <v>16</v>
       </c>
       <c r="N53" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O53">
         <v>512</v>
@@ -6434,7 +6409,7 @@
         <v>60</v>
       </c>
       <c r="U53" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V53">
         <v>5</v>
@@ -6443,7 +6418,7 @@
         <v>9.5</v>
       </c>
       <c r="X53" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z53">
         <f t="shared" si="6"/>
@@ -6466,18 +6441,18 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>37</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D54" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -6489,17 +6464,17 @@
         <v>69</v>
       </c>
       <c r="K54" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X54&lt;&gt;"쿠팡", ((J54-I54)/I54)*100, "")</f>
         <v/>
       </c>
       <c r="L54" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="M54">
         <v>16</v>
       </c>
       <c r="N54" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O54">
         <v>512</v>
@@ -6520,7 +6495,7 @@
         <v>70</v>
       </c>
       <c r="U54" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V54">
         <v>5</v>
@@ -6529,7 +6504,7 @@
         <v>10.25</v>
       </c>
       <c r="X54" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z54">
         <f t="shared" si="6"/>
@@ -6552,24 +6527,24 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D55" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -6578,17 +6553,17 @@
         <v>69</v>
       </c>
       <c r="K55" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X55&lt;&gt;"쿠팡", ((J55-I55)/I55)*100, "")</f>
         <v/>
       </c>
       <c r="L55" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="M55">
         <v>8</v>
       </c>
       <c r="N55" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O55">
         <v>256</v>
@@ -6609,7 +6584,7 @@
         <v>60</v>
       </c>
       <c r="U55" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V55">
         <v>6</v>
@@ -6618,7 +6593,7 @@
         <v>9.25</v>
       </c>
       <c r="X55" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z55">
         <f t="shared" si="6"/>
@@ -6641,24 +6616,24 @@
         <v>7.5949367088608E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>41</v>
       </c>
       <c r="B56" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -6667,17 +6642,17 @@
         <v>80</v>
       </c>
       <c r="K56" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X56&lt;&gt;"쿠팡", ((J56-I56)/I56)*100, "")</f>
         <v/>
       </c>
       <c r="L56" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="M56">
         <v>8</v>
       </c>
       <c r="N56" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O56">
         <v>256</v>
@@ -6698,7 +6673,7 @@
         <v>60</v>
       </c>
       <c r="U56" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V56">
         <v>6</v>
@@ -6707,7 +6682,7 @@
         <v>10.75</v>
       </c>
       <c r="X56" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z56">
         <f t="shared" si="6"/>
@@ -6730,24 +6705,24 @@
         <v>7.5949367088608E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>42</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D57" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -6756,17 +6731,17 @@
         <v>69</v>
       </c>
       <c r="K57" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X57&lt;&gt;"쿠팡", ((J57-I57)/I57)*100, "")</f>
         <v/>
       </c>
       <c r="L57" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="M57">
         <v>16</v>
       </c>
       <c r="N57" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O57">
         <v>256</v>
@@ -6787,7 +6762,7 @@
         <v>60</v>
       </c>
       <c r="U57" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V57">
         <v>6</v>
@@ -6796,7 +6771,7 @@
         <v>10.25</v>
       </c>
       <c r="X57" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z57">
         <f t="shared" si="6"/>
@@ -6819,18 +6794,18 @@
         <v>7.5949367088608E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>49</v>
       </c>
       <c r="B58" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D58" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -6842,17 +6817,17 @@
         <v>125</v>
       </c>
       <c r="K58" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X58&lt;&gt;"쿠팡", ((J58-I58)/I58)*100, "")</f>
         <v/>
       </c>
       <c r="L58" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M58">
         <v>32</v>
       </c>
       <c r="N58" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O58">
         <v>512</v>
@@ -6873,7 +6848,7 @@
         <v>60</v>
       </c>
       <c r="U58" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V58">
         <v>7</v>
@@ -6882,7 +6857,7 @@
         <v>10</v>
       </c>
       <c r="X58" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z58">
         <f t="shared" si="6"/>
@@ -6905,18 +6880,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D59" t="s">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -6928,17 +6903,17 @@
         <v>74</v>
       </c>
       <c r="K59" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(X59&lt;&gt;"쿠팡", ((J59-I59)/I59)*100, "")</f>
         <v/>
       </c>
       <c r="L59" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="M59">
         <v>16</v>
       </c>
       <c r="N59" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O59">
         <v>512</v>
@@ -6959,7 +6934,7 @@
         <v>60</v>
       </c>
       <c r="U59" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V59">
         <v>5</v>
@@ -6968,7 +6943,7 @@
         <v>9.5</v>
       </c>
       <c r="X59" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z59">
         <f t="shared" si="6"/>
@@ -6991,18 +6966,18 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="C60" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D60" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -7018,13 +6993,13 @@
         <v/>
       </c>
       <c r="L60" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="M60">
         <v>16</v>
       </c>
       <c r="N60" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O60">
         <v>512</v>
@@ -7045,7 +7020,7 @@
         <v>70</v>
       </c>
       <c r="U60" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V60">
         <v>5</v>
@@ -7054,7 +7029,7 @@
         <v>10.25</v>
       </c>
       <c r="X60" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z60">
         <f t="shared" si="6"/>
@@ -7077,18 +7052,18 @@
         <v>-0.924050632911392</v>
       </c>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="C61" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D61" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -7104,13 +7079,13 @@
         <v/>
       </c>
       <c r="L61" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M61">
         <v>16</v>
       </c>
       <c r="N61" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O61">
         <v>1024</v>
@@ -7131,7 +7106,7 @@
         <v>71</v>
       </c>
       <c r="U61" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V61">
         <v>7</v>
@@ -7140,7 +7115,7 @@
         <v>9.5</v>
       </c>
       <c r="X61" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z61">
         <f t="shared" si="6"/>
@@ -7163,18 +7138,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>47</v>
       </c>
       <c r="B62" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D62" t="s">
-        <v>153</v>
+        <v>203</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -7190,13 +7165,13 @@
         <v/>
       </c>
       <c r="L62" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M62">
         <v>24</v>
       </c>
       <c r="N62" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O62">
         <v>512</v>
@@ -7217,7 +7192,7 @@
         <v>60</v>
       </c>
       <c r="U62" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V62">
         <v>7</v>
@@ -7226,7 +7201,7 @@
         <v>8.5</v>
       </c>
       <c r="X62" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z62">
         <f t="shared" si="6"/>
@@ -7249,18 +7224,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>50</v>
       </c>
       <c r="B63" t="s">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="C63" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D63" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -7276,13 +7251,13 @@
         <v/>
       </c>
       <c r="L63" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M63">
         <v>24</v>
       </c>
       <c r="N63" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O63">
         <v>512</v>
@@ -7303,7 +7278,7 @@
         <v>60</v>
       </c>
       <c r="U63" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V63">
         <v>7</v>
@@ -7312,7 +7287,7 @@
         <v>10</v>
       </c>
       <c r="X63" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z63">
         <f t="shared" si="6"/>
@@ -7335,24 +7310,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>53</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="C64" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D64" t="s">
-        <v>164</v>
+        <v>224</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -7365,13 +7340,13 @@
         <v/>
       </c>
       <c r="L64" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M64">
         <v>32</v>
       </c>
       <c r="N64" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O64">
         <v>512</v>
@@ -7392,7 +7367,7 @@
         <v>70</v>
       </c>
       <c r="U64" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V64">
         <v>7</v>
@@ -7401,7 +7376,7 @@
         <v>7.25</v>
       </c>
       <c r="X64" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z64">
         <f t="shared" si="6"/>
@@ -7424,24 +7399,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>54</v>
       </c>
       <c r="B65" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="C65" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D65" t="s">
-        <v>164</v>
+        <v>224</v>
       </c>
       <c r="E65">
         <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -7454,13 +7429,13 @@
         <v/>
       </c>
       <c r="L65" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M65">
         <v>32</v>
       </c>
       <c r="N65" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O65">
         <v>1024</v>
@@ -7481,7 +7456,7 @@
         <v>70</v>
       </c>
       <c r="U65" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V65">
         <v>7</v>
@@ -7490,7 +7465,7 @@
         <v>7.25</v>
       </c>
       <c r="X65" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z65">
         <f t="shared" si="6"/>
@@ -7513,18 +7488,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>57</v>
       </c>
       <c r="B66" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="C66" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D66" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -7540,13 +7515,13 @@
         <v/>
       </c>
       <c r="L66" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="M66">
         <v>32</v>
       </c>
       <c r="N66" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O66">
         <v>1024</v>
@@ -7567,7 +7542,7 @@
         <v>70</v>
       </c>
       <c r="U66" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V66">
         <v>7</v>
@@ -7576,14 +7551,14 @@
         <v>7.25</v>
       </c>
       <c r="X66" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z66">
         <f t="shared" ref="Z66:Z80" si="11">T66/W66</f>
         <v>9.6551724137931032</v>
       </c>
       <c r="AA66">
-        <f t="shared" ref="AA66:AA97" si="12">Z66-(AVERAGE(Z:Z))</f>
+        <f t="shared" ref="AA66:AA80" si="12">Z66-(AVERAGE(Z:Z))</f>
         <v>2.2160517851130086</v>
       </c>
       <c r="AB66">
@@ -7599,24 +7574,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="C67" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D67" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -7629,13 +7604,13 @@
         <v/>
       </c>
       <c r="L67" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
       <c r="M67">
         <v>32</v>
       </c>
       <c r="N67" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O67">
         <v>512</v>
@@ -7656,7 +7631,7 @@
         <v>70</v>
       </c>
       <c r="U67" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V67">
         <v>8</v>
@@ -7665,7 +7640,7 @@
         <v>7.25</v>
       </c>
       <c r="X67" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z67">
         <f t="shared" si="11"/>
@@ -7688,24 +7663,24 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>56</v>
       </c>
       <c r="B68" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D68" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E68">
         <v>2</v>
       </c>
       <c r="F68" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -7718,13 +7693,13 @@
         <v/>
       </c>
       <c r="L68" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
       <c r="M68">
         <v>32</v>
       </c>
       <c r="N68" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O68">
         <v>1024</v>
@@ -7745,7 +7720,7 @@
         <v>70</v>
       </c>
       <c r="U68" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V68">
         <v>8</v>
@@ -7754,7 +7729,7 @@
         <v>7.25</v>
       </c>
       <c r="X68" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z68">
         <f t="shared" si="11"/>
@@ -7777,18 +7752,18 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>60</v>
       </c>
       <c r="B69" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="C69" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D69" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -7804,13 +7779,13 @@
         <v/>
       </c>
       <c r="L69" t="s">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="M69">
         <v>32</v>
       </c>
       <c r="N69" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O69">
         <v>1024</v>
@@ -7831,7 +7806,7 @@
         <v>80</v>
       </c>
       <c r="U69" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V69">
         <v>4</v>
@@ -7840,7 +7815,7 @@
         <v>9.5</v>
       </c>
       <c r="X69" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z69">
         <f t="shared" si="11"/>
@@ -7863,18 +7838,18 @@
         <v>-1.924050632911392</v>
       </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="C70" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D70" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -7886,17 +7861,17 @@
         <v>125</v>
       </c>
       <c r="K70" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(X70&lt;&gt;"쿠팡", ((J70-I70)/I70)*100, "")</f>
         <v/>
       </c>
       <c r="L70" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="M70">
         <v>24</v>
       </c>
       <c r="N70" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="O70">
         <v>512</v>
@@ -7917,7 +7892,7 @@
         <v>60</v>
       </c>
       <c r="U70" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V70">
         <v>8</v>
@@ -7926,7 +7901,7 @@
         <v>10</v>
       </c>
       <c r="X70" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z70">
         <f t="shared" si="11"/>
@@ -7949,18 +7924,18 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>58</v>
       </c>
       <c r="B71" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="C71" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D71" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -7972,17 +7947,17 @@
         <v>176</v>
       </c>
       <c r="K71" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(X71&lt;&gt;"쿠팡", ((J71-I71)/I71)*100, "")</f>
         <v/>
       </c>
       <c r="L71" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M71">
         <v>32</v>
       </c>
       <c r="N71" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O71">
         <v>512</v>
@@ -8003,7 +7978,7 @@
         <v>70</v>
       </c>
       <c r="U71" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V71">
         <v>8</v>
@@ -8012,7 +7987,7 @@
         <v>7.25</v>
       </c>
       <c r="X71" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z71">
         <f t="shared" si="11"/>
@@ -8035,18 +8010,18 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>59</v>
       </c>
       <c r="B72" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="C72" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="D72" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -8058,17 +8033,17 @@
         <v>187</v>
       </c>
       <c r="K72" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(X72&lt;&gt;"쿠팡", ((J72-I72)/I72)*100, "")</f>
         <v/>
       </c>
       <c r="L72" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M72">
         <v>32</v>
       </c>
       <c r="N72" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O72">
         <v>1024</v>
@@ -8089,7 +8064,7 @@
         <v>70</v>
       </c>
       <c r="U72" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V72">
         <v>8</v>
@@ -8098,7 +8073,7 @@
         <v>7.5</v>
       </c>
       <c r="X72" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z72">
         <f t="shared" si="11"/>
@@ -8121,18 +8096,18 @@
         <v>2.075949367088608</v>
       </c>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>181</v>
+        <v>126</v>
       </c>
       <c r="C73" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="D73" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -8144,17 +8119,17 @@
         <v>139</v>
       </c>
       <c r="K73" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(X73&lt;&gt;"쿠팡", ((J73-I73)/I73)*100, "")</f>
         <v/>
       </c>
       <c r="L73" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M73">
         <v>16</v>
       </c>
       <c r="N73" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O73">
         <v>256</v>
@@ -8175,7 +8150,7 @@
         <v>72</v>
       </c>
       <c r="U73" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V73">
         <v>7</v>
@@ -8184,7 +8159,7 @@
         <v>8</v>
       </c>
       <c r="X73" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z73">
         <f t="shared" si="11"/>
@@ -8207,18 +8182,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>69</v>
       </c>
       <c r="B74" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="C74" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="D74" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -8230,17 +8205,17 @@
         <v>176</v>
       </c>
       <c r="K74" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(X74&lt;&gt;"쿠팡", ((J74-I74)/I74)*100, "")</f>
         <v/>
       </c>
       <c r="L74" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M74">
         <v>16</v>
       </c>
       <c r="N74" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O74">
         <v>256</v>
@@ -8261,7 +8236,7 @@
         <v>77</v>
       </c>
       <c r="U74" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V74">
         <v>7</v>
@@ -8270,7 +8245,7 @@
         <v>9.5</v>
       </c>
       <c r="X74" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z74">
         <f t="shared" si="11"/>
@@ -8293,18 +8268,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>72</v>
       </c>
       <c r="B75" t="s">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="C75" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="D75" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -8316,17 +8291,17 @@
         <v>187</v>
       </c>
       <c r="K75" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(X75&lt;&gt;"쿠팡", ((J75-I75)/I75)*100, "")</f>
         <v/>
       </c>
       <c r="L75" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M75">
         <v>16</v>
       </c>
       <c r="N75" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O75">
         <v>256</v>
@@ -8347,7 +8322,7 @@
         <v>77</v>
       </c>
       <c r="U75" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V75">
         <v>7</v>
@@ -8356,7 +8331,7 @@
         <v>9.5</v>
       </c>
       <c r="X75" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z75">
         <f t="shared" si="11"/>
@@ -8379,18 +8354,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>73</v>
       </c>
       <c r="B76" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="C76" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="D76" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -8402,17 +8377,17 @@
         <v>176</v>
       </c>
       <c r="K76" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(X76&lt;&gt;"쿠팡", ((J76-I76)/I76)*100, "")</f>
         <v/>
       </c>
       <c r="L76" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M76">
         <v>16</v>
       </c>
       <c r="N76" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O76">
         <v>256</v>
@@ -8433,7 +8408,7 @@
         <v>77</v>
       </c>
       <c r="U76" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V76">
         <v>7</v>
@@ -8442,7 +8417,7 @@
         <v>9.5</v>
       </c>
       <c r="X76" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z76">
         <f t="shared" si="11"/>
@@ -8465,24 +8440,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>70</v>
       </c>
       <c r="B77" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="C77" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="D77" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>188</v>
+        <v>129</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -8491,17 +8466,17 @@
         <v>181</v>
       </c>
       <c r="K77" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(X77&lt;&gt;"쿠팡", ((J77-I77)/I77)*100, "")</f>
         <v/>
       </c>
       <c r="L77" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M77">
         <v>16</v>
       </c>
       <c r="N77" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O77">
         <v>256</v>
@@ -8522,7 +8497,7 @@
         <v>77</v>
       </c>
       <c r="U77" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V77">
         <v>7</v>
@@ -8531,7 +8506,7 @@
         <v>7.5</v>
       </c>
       <c r="X77" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z77">
         <f t="shared" si="11"/>
@@ -8554,24 +8529,24 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>71</v>
       </c>
       <c r="B78" t="s">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="C78" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="D78" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>190</v>
+        <v>131</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -8580,17 +8555,17 @@
         <v>181</v>
       </c>
       <c r="K78" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(X78&lt;&gt;"쿠팡", ((J78-I78)/I78)*100, "")</f>
         <v/>
       </c>
       <c r="L78" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M78">
         <v>16</v>
       </c>
       <c r="N78" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O78">
         <v>256</v>
@@ -8611,7 +8586,7 @@
         <v>77</v>
       </c>
       <c r="U78" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V78">
         <v>7</v>
@@ -8620,7 +8595,7 @@
         <v>7.5</v>
       </c>
       <c r="X78" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z78">
         <f t="shared" si="11"/>
@@ -8643,18 +8618,18 @@
         <v>1.075949367088608</v>
       </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>74</v>
       </c>
       <c r="B79" t="s">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="C79" t="s">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="D79" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -8666,17 +8641,17 @@
         <v>110</v>
       </c>
       <c r="K79" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(X79&lt;&gt;"쿠팡", ((J79-I79)/I79)*100, "")</f>
         <v/>
       </c>
       <c r="L79" t="s">
-        <v>198</v>
+        <v>136</v>
       </c>
       <c r="M79">
         <v>16</v>
       </c>
       <c r="N79" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O79">
         <v>256</v>
@@ -8697,7 +8672,7 @@
         <v>48</v>
       </c>
       <c r="U79" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V79">
         <v>3</v>
@@ -8706,7 +8681,7 @@
         <v>5.5</v>
       </c>
       <c r="X79" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z79">
         <f t="shared" si="11"/>
@@ -8729,18 +8704,18 @@
         <v>-2.924050632911392</v>
       </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>75</v>
       </c>
       <c r="B80" t="s">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="C80" t="s">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="D80" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="E80">
         <v>1</v>
@@ -8756,13 +8731,13 @@
         <v/>
       </c>
       <c r="L80" t="s">
-        <v>201</v>
+        <v>138</v>
       </c>
       <c r="M80">
         <v>16</v>
       </c>
       <c r="N80" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O80">
         <v>512</v>
@@ -8783,7 +8758,7 @@
         <v>54</v>
       </c>
       <c r="U80" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="V80">
         <v>3</v>
@@ -8792,7 +8767,7 @@
         <v>5.5</v>
       </c>
       <c r="X80" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z80">
         <f t="shared" si="11"/>
@@ -8824,7 +8799,7 @@
     <hyperlink ref="B4" r:id="rId1" xr:uid="{8CDE4958-5903-431C-B34F-E9CA79951BCF}"/>
     <hyperlink ref="B5" r:id="rId2" xr:uid="{7C4169E8-93C9-4878-A0A7-F2E43E78EFA2}"/>
     <hyperlink ref="B7" r:id="rId3" xr:uid="{C68D053D-6A31-45F0-9494-12AE26E861B2}"/>
-    <hyperlink ref="B9" r:id="rId4" xr:uid="{836DAA7E-3698-46B3-956C-2D7F97CE46FB}"/>
+    <hyperlink ref="B9" r:id="rId4" display="https://smartstore.naver.com/samsung_mall/products/11256046363" xr:uid="{836DAA7E-3698-46B3-956C-2D7F97CE46FB}"/>
     <hyperlink ref="B8" r:id="rId5" xr:uid="{637EE4E2-122C-4B62-A3AA-BF8885E38863}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/manualdata/_manualdata_master.xlsx
+++ b/data/manualdata/_manualdata_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\notebookpick\data\manualdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0171FC-DCAC-4713-A939-76C918CB766F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F4B619-ABFE-492D-A8A7-2AE81804313C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{52B35C0C-4AC1-4CD7-A119-F59BBD510595}"/>
   </bookViews>
@@ -167,6 +167,9 @@
     <t>https://www.coupang.com/vp/products/8579806173?itemId=24867355094&amp;vendorItemId=91874318252</t>
   </si>
   <si>
+    <t>asus</t>
+  </si>
+  <si>
     <t>[ARM] 젠북 A14, X1-26</t>
   </si>
   <si>
@@ -236,6 +239,9 @@
     <t>https://www.coupang.com/vp/products/8620630703?itemId=25010066108&amp;vendorItemId=92015050332</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
     <t>i5 1334u</t>
   </si>
   <si>
@@ -299,6 +305,9 @@
     <t>https://www.coupang.com/vp/products/9088545835?itemId=26706196132&amp;vendorItemId=93677980039</t>
   </si>
   <si>
+    <t>lenovo</t>
+  </si>
+  <si>
     <t>r3 7320u</t>
   </si>
   <si>
@@ -414,6 +423,9 @@
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8518435229?itemId=24662380297&amp;vendorItemId=91672792964</t>
+  </si>
+  <si>
+    <t>lg</t>
   </si>
   <si>
     <t>https://www.coupang.com/vp/products/8518435238?itemId=24662380338&amp;vendorItemId=91672792997</t>
@@ -496,10 +508,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>msi</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>후면포트</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -765,9 +773,6 @@
     <t>요가 7 2in1 14ILL10, U7 258V</t>
   </si>
   <si>
-    <t>Lenovo</t>
-  </si>
-  <si>
     <t>www.Lenovo.com/kr/ko/p/laptops/thinkpad/thinkpadx/thinkpad-x13-gen-6-13-inch-intel/21rkcto1wwkr3</t>
   </si>
   <si>
@@ -778,25 +783,19 @@
   </si>
   <si>
     <t>www.Lenovo.com/kr/ko/p/laptops/thinkpad/thinkpade/thinkpad-e14-gen-7-14-inch-intel-laptop/21u2cto1wwkr2</t>
-  </si>
-  <si>
-    <t>ASUS</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>LG</t>
   </si>
   <si>
     <t>last_update</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>SAMSUNG</t>
-  </si>
-  <si>
     <t>https://smartstore.naver.com/SAMSUNG_mall/products/11256046363</t>
+  </si>
+  <si>
+    <t>msi</t>
+  </si>
+  <si>
+    <t>samsung</t>
   </si>
 </sst>
 </file>
@@ -1790,7 +1789,8 @@
   <dimension ref="A1:AD80"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="11.640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="102.0703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.640625" customWidth="1"/>
     <col min="4" max="4" width="40.85546875" customWidth="1"/>
     <col min="8" max="8" width="10.640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1807,7 +1807,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1819,7 +1819,7 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
@@ -1843,7 +1843,7 @@
         <v>12</v>
       </c>
       <c r="P1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q1" t="s">
         <v>13</v>
@@ -1870,7 +1870,7 @@
         <v>20</v>
       </c>
       <c r="Y1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Z1" t="s">
         <v>21</v>
@@ -1893,13 +1893,13 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1918,13 +1918,13 @@
         <v>-7.1428571428571423</v>
       </c>
       <c r="L2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M2">
         <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="O2">
         <v>512</v>
@@ -1945,7 +1945,7 @@
         <v>75</v>
       </c>
       <c r="U2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="V2">
         <v>7</v>
@@ -1954,7 +1954,7 @@
         <v>9.5</v>
       </c>
       <c r="X2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Z2">
         <f t="shared" ref="Z2:Z33" si="0">T2/W2</f>
@@ -1982,13 +1982,13 @@
         <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -2010,7 +2010,7 @@
         <v>-11.111111111111111</v>
       </c>
       <c r="L3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M3">
         <v>8</v>
@@ -2046,7 +2046,7 @@
         <v>11</v>
       </c>
       <c r="X3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Z3">
         <f t="shared" si="0"/>
@@ -2074,13 +2074,13 @@
         <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2095,7 +2095,7 @@
         <v>118</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K3:K66" si="5">IF(X4&lt;&gt;"쿠팡", ((J4-I4)/I4)*100, "")</f>
+        <f t="shared" ref="K4:K66" si="5">IF(X4&lt;&gt;"쿠팡", ((J4-I4)/I4)*100, "")</f>
         <v>-5.6000000000000005</v>
       </c>
       <c r="L4" t="s">
@@ -2105,7 +2105,7 @@
         <v>32</v>
       </c>
       <c r="N4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O4">
         <v>512</v>
@@ -2135,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="X4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
@@ -2163,19 +2163,19 @@
         <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -2191,7 +2191,7 @@
         <v>-10.625</v>
       </c>
       <c r="L5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M5">
         <v>32</v>
@@ -2227,7 +2227,7 @@
         <v>7.25</v>
       </c>
       <c r="X5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
@@ -2255,19 +2255,19 @@
         <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>243</v>
       </c>
       <c r="D6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -2283,13 +2283,13 @@
         <v>-7.6923076923076925</v>
       </c>
       <c r="L6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M6">
         <v>16</v>
       </c>
       <c r="N6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="O6">
         <v>512</v>
@@ -2310,7 +2310,7 @@
         <v>100</v>
       </c>
       <c r="U6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -2319,7 +2319,7 @@
         <v>10.25</v>
       </c>
       <c r="X6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Z6">
         <f t="shared" si="0"/>
@@ -2347,13 +2347,13 @@
         <v>77</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2372,13 +2372,13 @@
         <v>8.5714285714285712</v>
       </c>
       <c r="L7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M7">
         <v>16</v>
       </c>
       <c r="N7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="O7">
         <v>256</v>
@@ -2399,7 +2399,7 @@
         <v>54</v>
       </c>
       <c r="U7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="V7">
         <v>3</v>
@@ -2408,7 +2408,7 @@
         <v>10.25</v>
       </c>
       <c r="X7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
@@ -2436,13 +2436,13 @@
         <v>79</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2461,13 +2461,13 @@
         <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="O8">
         <v>256</v>
@@ -2488,7 +2488,7 @@
         <v>76</v>
       </c>
       <c r="U8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -2497,7 +2497,7 @@
         <v>7.5</v>
       </c>
       <c r="X8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Z8">
         <f t="shared" si="0"/>
@@ -2525,13 +2525,13 @@
         <v>78</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" t="s">
         <v>244</v>
       </c>
-      <c r="C9" t="s">
-        <v>243</v>
-      </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -2550,13 +2550,13 @@
         <v>9.0909090909090917</v>
       </c>
       <c r="L9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M9">
         <v>16</v>
       </c>
       <c r="N9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="O9">
         <v>256</v>
@@ -2577,7 +2577,7 @@
         <v>63</v>
       </c>
       <c r="U9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -2586,7 +2586,7 @@
         <v>6.75</v>
       </c>
       <c r="X9" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
@@ -2614,19 +2614,19 @@
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C10" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>6.25</v>
       </c>
       <c r="L10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M10">
         <v>32</v>
       </c>
       <c r="N10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="O10">
         <v>256</v>
@@ -2669,7 +2669,7 @@
         <v>55</v>
       </c>
       <c r="U10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -2678,7 +2678,7 @@
         <v>6</v>
       </c>
       <c r="X10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="Z10">
         <f t="shared" si="0"/>
@@ -2706,19 +2706,19 @@
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C11" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2734,13 +2734,13 @@
         <v>-6.4</v>
       </c>
       <c r="L11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M11">
         <v>16</v>
       </c>
       <c r="N11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="O11">
         <v>256</v>
@@ -2761,7 +2761,7 @@
         <v>64</v>
       </c>
       <c r="U11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -2770,7 +2770,7 @@
         <v>7.5</v>
       </c>
       <c r="X11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="Z11">
         <f t="shared" si="0"/>
@@ -2798,19 +2798,19 @@
         <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C12" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2826,13 +2826,13 @@
         <v>-5.1282051282051277</v>
       </c>
       <c r="L12" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M12">
         <v>32</v>
       </c>
       <c r="N12" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="O12">
         <v>512</v>
@@ -2853,7 +2853,7 @@
         <v>80</v>
       </c>
       <c r="U12" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -2862,7 +2862,7 @@
         <v>7.5</v>
       </c>
       <c r="X12" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="Z12">
         <f t="shared" si="0"/>
@@ -2890,19 +2890,19 @@
         <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C13" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2918,13 +2918,13 @@
         <v>-1.4814814814814816</v>
       </c>
       <c r="L13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M13">
         <v>32</v>
       </c>
       <c r="N13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="O13">
         <v>512</v>
@@ -2945,7 +2945,7 @@
         <v>64</v>
       </c>
       <c r="U13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -2954,7 +2954,7 @@
         <v>6.75</v>
       </c>
       <c r="X13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="Z13">
         <f t="shared" si="0"/>
@@ -2988,7 +2988,7 @@
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -3077,7 +3077,7 @@
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -3166,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -3338,7 +3338,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -3418,13 +3418,13 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -3443,7 +3443,7 @@
         <v/>
       </c>
       <c r="L19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -3507,13 +3507,13 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="L20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M20">
         <v>16</v>
@@ -3593,13 +3593,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -3615,7 +3615,7 @@
         <v/>
       </c>
       <c r="L21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M21">
         <v>16</v>
@@ -3679,13 +3679,13 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -3701,7 +3701,7 @@
         <v/>
       </c>
       <c r="L22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M22">
         <v>16</v>
@@ -3765,13 +3765,13 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -3851,13 +3851,13 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -3937,19 +3937,19 @@
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3962,13 +3962,13 @@
         <v/>
       </c>
       <c r="L25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M25">
         <v>16</v>
       </c>
       <c r="N25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O25">
         <v>512</v>
@@ -4026,19 +4026,19 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -4051,13 +4051,13 @@
         <v/>
       </c>
       <c r="L26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M26">
         <v>16</v>
       </c>
       <c r="N26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O26">
         <v>512</v>
@@ -4115,13 +4115,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="L27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M27">
         <v>16</v>
       </c>
       <c r="N27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O27">
         <v>512</v>
@@ -4201,13 +4201,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -4223,13 +4223,13 @@
         <v/>
       </c>
       <c r="L28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M28">
         <v>32</v>
       </c>
       <c r="N28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O28">
         <v>512</v>
@@ -4287,13 +4287,13 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -4315,7 +4315,7 @@
         <v>32</v>
       </c>
       <c r="N29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O29">
         <v>1024</v>
@@ -4376,10 +4376,10 @@
         <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -4395,7 +4395,7 @@
         <v/>
       </c>
       <c r="L30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M30">
         <v>16</v>
@@ -4459,13 +4459,13 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -4481,13 +4481,13 @@
         <v/>
       </c>
       <c r="L31" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M31">
         <v>8</v>
       </c>
       <c r="N31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O31">
         <v>256</v>
@@ -4545,13 +4545,13 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -4570,7 +4570,7 @@
         <v/>
       </c>
       <c r="L32" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M32">
         <v>8</v>
@@ -4634,13 +4634,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -4656,7 +4656,7 @@
         <v/>
       </c>
       <c r="L33" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M33">
         <v>16</v>
@@ -4720,13 +4720,13 @@
         <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -4742,7 +4742,7 @@
         <v/>
       </c>
       <c r="L34" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M34">
         <v>16</v>
@@ -4806,13 +4806,13 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" t="s">
         <v>68</v>
       </c>
-      <c r="C35" t="s">
-        <v>240</v>
-      </c>
       <c r="D35" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -4831,7 +4831,7 @@
         <v/>
       </c>
       <c r="L35" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M35">
         <v>8</v>
@@ -4895,13 +4895,13 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -4917,7 +4917,7 @@
         <v/>
       </c>
       <c r="L36" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M36">
         <v>8</v>
@@ -4981,13 +4981,13 @@
         <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D37" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -5003,13 +5003,13 @@
         <v/>
       </c>
       <c r="L37" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="M37">
         <v>16</v>
       </c>
       <c r="N37" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O37">
         <v>256</v>
@@ -5067,13 +5067,13 @@
         <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -5089,7 +5089,7 @@
         <v/>
       </c>
       <c r="L38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M38">
         <v>32</v>
@@ -5153,13 +5153,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5175,7 +5175,7 @@
         <v/>
       </c>
       <c r="L39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M39">
         <v>16</v>
@@ -5239,13 +5239,13 @@
         <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D40" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -5261,7 +5261,7 @@
         <v/>
       </c>
       <c r="L40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M40">
         <v>16</v>
@@ -5325,13 +5325,13 @@
         <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D41" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -5347,7 +5347,7 @@
         <v/>
       </c>
       <c r="L41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M41">
         <v>16</v>
@@ -5411,13 +5411,13 @@
         <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D42" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -5433,7 +5433,7 @@
         <v/>
       </c>
       <c r="L42" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M42">
         <v>32</v>
@@ -5497,13 +5497,13 @@
         <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D43" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -5583,13 +5583,13 @@
         <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="D44" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -5669,13 +5669,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -5691,7 +5691,7 @@
         <v/>
       </c>
       <c r="L45" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M45">
         <v>8</v>
@@ -5755,13 +5755,13 @@
         <v>34</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -5777,7 +5777,7 @@
         <v/>
       </c>
       <c r="L46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M46">
         <v>16</v>
@@ -5841,13 +5841,13 @@
         <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D47" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -5863,7 +5863,7 @@
         <v/>
       </c>
       <c r="L47" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M47">
         <v>16</v>
@@ -5927,13 +5927,13 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C48" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D48" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -5949,13 +5949,13 @@
         <v/>
       </c>
       <c r="L48" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M48">
         <v>24</v>
       </c>
       <c r="N48" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O48">
         <v>512</v>
@@ -6013,13 +6013,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C49" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D49" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -6035,13 +6035,13 @@
         <v/>
       </c>
       <c r="L49" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M49">
         <v>24</v>
       </c>
       <c r="N49" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O49">
         <v>512</v>
@@ -6099,13 +6099,13 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -6121,13 +6121,13 @@
         <v/>
       </c>
       <c r="L50" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M50">
         <v>32</v>
       </c>
       <c r="N50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O50">
         <v>512</v>
@@ -6185,13 +6185,13 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C51" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D51" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -6207,7 +6207,7 @@
         <v/>
       </c>
       <c r="L51" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M51">
         <v>16</v>
@@ -6271,13 +6271,13 @@
         <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C52" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D52" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -6296,7 +6296,7 @@
         <v/>
       </c>
       <c r="L52" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M52">
         <v>8</v>
@@ -6360,13 +6360,13 @@
         <v>35</v>
       </c>
       <c r="B53" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C53" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D53" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -6382,7 +6382,7 @@
         <v/>
       </c>
       <c r="L53" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M53">
         <v>16</v>
@@ -6446,13 +6446,13 @@
         <v>37</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C54" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D54" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -6468,7 +6468,7 @@
         <v/>
       </c>
       <c r="L54" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M54">
         <v>16</v>
@@ -6532,13 +6532,13 @@
         <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C55" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D55" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -6557,7 +6557,7 @@
         <v/>
       </c>
       <c r="L55" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M55">
         <v>8</v>
@@ -6621,13 +6621,13 @@
         <v>41</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C56" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D56" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -6646,7 +6646,7 @@
         <v/>
       </c>
       <c r="L56" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M56">
         <v>8</v>
@@ -6710,13 +6710,13 @@
         <v>42</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C57" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D57" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -6735,13 +6735,13 @@
         <v/>
       </c>
       <c r="L57" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M57">
         <v>16</v>
       </c>
       <c r="N57" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O57">
         <v>256</v>
@@ -6799,13 +6799,13 @@
         <v>49</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D58" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -6821,13 +6821,13 @@
         <v/>
       </c>
       <c r="L58" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M58">
         <v>32</v>
       </c>
       <c r="N58" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O58">
         <v>512</v>
@@ -6885,13 +6885,13 @@
         <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C59" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D59" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -6907,7 +6907,7 @@
         <v/>
       </c>
       <c r="L59" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M59">
         <v>16</v>
@@ -6971,13 +6971,13 @@
         <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C60" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -6993,7 +6993,7 @@
         <v/>
       </c>
       <c r="L60" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M60">
         <v>16</v>
@@ -7057,13 +7057,13 @@
         <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C61" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D61" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -7143,13 +7143,13 @@
         <v>47</v>
       </c>
       <c r="B62" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C62" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D62" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -7171,7 +7171,7 @@
         <v>24</v>
       </c>
       <c r="N62" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O62">
         <v>512</v>
@@ -7229,13 +7229,13 @@
         <v>50</v>
       </c>
       <c r="B63" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C63" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D63" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -7257,7 +7257,7 @@
         <v>24</v>
       </c>
       <c r="N63" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O63">
         <v>512</v>
@@ -7315,19 +7315,19 @@
         <v>53</v>
       </c>
       <c r="B64" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C64" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D64" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -7340,7 +7340,7 @@
         <v/>
       </c>
       <c r="L64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M64">
         <v>32</v>
@@ -7404,19 +7404,19 @@
         <v>54</v>
       </c>
       <c r="B65" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C65" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D65" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E65">
         <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -7429,7 +7429,7 @@
         <v/>
       </c>
       <c r="L65" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M65">
         <v>32</v>
@@ -7493,13 +7493,13 @@
         <v>57</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C66" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D66" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -7515,7 +7515,7 @@
         <v/>
       </c>
       <c r="L66" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M66">
         <v>32</v>
@@ -7579,19 +7579,19 @@
         <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C67" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D67" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -7604,7 +7604,7 @@
         <v/>
       </c>
       <c r="L67" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="M67">
         <v>32</v>
@@ -7668,19 +7668,19 @@
         <v>56</v>
       </c>
       <c r="B68" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C68" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D68" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E68">
         <v>2</v>
       </c>
       <c r="F68" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -7693,7 +7693,7 @@
         <v/>
       </c>
       <c r="L68" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="M68">
         <v>32</v>
@@ -7757,13 +7757,13 @@
         <v>60</v>
       </c>
       <c r="B69" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C69" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D69" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -7779,7 +7779,7 @@
         <v/>
       </c>
       <c r="L69" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M69">
         <v>32</v>
@@ -7843,13 +7843,13 @@
         <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C70" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D70" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -7865,13 +7865,13 @@
         <v/>
       </c>
       <c r="L70" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M70">
         <v>24</v>
       </c>
       <c r="N70" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O70">
         <v>512</v>
@@ -7929,13 +7929,13 @@
         <v>58</v>
       </c>
       <c r="B71" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C71" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D71" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -8015,13 +8015,13 @@
         <v>59</v>
       </c>
       <c r="B72" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C72" t="s">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="D72" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -8101,13 +8101,13 @@
         <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>241</v>
+        <v>130</v>
       </c>
       <c r="D73" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -8187,13 +8187,13 @@
         <v>69</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C74" t="s">
-        <v>241</v>
+        <v>130</v>
       </c>
       <c r="D74" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -8273,13 +8273,13 @@
         <v>72</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C75" t="s">
-        <v>241</v>
+        <v>130</v>
       </c>
       <c r="D75" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -8359,13 +8359,13 @@
         <v>73</v>
       </c>
       <c r="B76" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C76" t="s">
-        <v>241</v>
+        <v>130</v>
       </c>
       <c r="D76" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -8445,19 +8445,19 @@
         <v>70</v>
       </c>
       <c r="B77" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C77" t="s">
-        <v>241</v>
+        <v>130</v>
       </c>
       <c r="D77" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -8470,7 +8470,7 @@
         <v/>
       </c>
       <c r="L77" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M77">
         <v>16</v>
@@ -8534,19 +8534,19 @@
         <v>71</v>
       </c>
       <c r="B78" t="s">
+        <v>134</v>
+      </c>
+      <c r="C78" t="s">
         <v>130</v>
       </c>
-      <c r="C78" t="s">
-        <v>241</v>
-      </c>
       <c r="D78" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -8559,7 +8559,7 @@
         <v/>
       </c>
       <c r="L78" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M78">
         <v>16</v>
@@ -8623,13 +8623,13 @@
         <v>74</v>
       </c>
       <c r="B79" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C79" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D79" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -8645,7 +8645,7 @@
         <v/>
       </c>
       <c r="L79" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="M79">
         <v>16</v>
@@ -8709,13 +8709,13 @@
         <v>75</v>
       </c>
       <c r="B80" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C80" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D80" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E80">
         <v>1</v>
@@ -8731,7 +8731,7 @@
         <v/>
       </c>
       <c r="L80" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M80">
         <v>16</v>
